--- a/database/event/1978/event_1978_evp_summary.xlsx
+++ b/database/event/1978/event_1978_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.2775</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5106</v>
+        <v>2.4476</v>
       </c>
       <c r="E2" t="n">
         <v>7.2577</v>
@@ -548,7 +548,7 @@
         <v>3.8175</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1953</v>
+        <v>2.1366</v>
       </c>
       <c r="E3" t="n">
         <v>6.4773</v>
@@ -594,7 +594,7 @@
         <v>3.7802</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1697</v>
+        <v>2.1114</v>
       </c>
       <c r="E4" t="n">
         <v>6.4139</v>
@@ -640,7 +640,7 @@
         <v>2.7956</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4948</v>
+        <v>1.4458</v>
       </c>
       <c r="E5" t="n">
         <v>4.7433</v>
@@ -686,7 +686,7 @@
         <v>2.4531</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2601</v>
+        <v>1.2144</v>
       </c>
       <c r="E6" t="n">
         <v>4.1623</v>
@@ -732,7 +732,7 @@
         <v>2.3697</v>
       </c>
       <c r="D7" t="n">
-        <v>1.203</v>
+        <v>1.158</v>
       </c>
       <c r="E7" t="n">
         <v>4.0208</v>
@@ -778,7 +778,7 @@
         <v>2.247</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1188</v>
+        <v>1.075</v>
       </c>
       <c r="E8" t="n">
         <v>3.8125</v>
@@ -824,7 +824,7 @@
         <v>2.1251</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0353</v>
+        <v>0.9926</v>
       </c>
       <c r="E9" t="n">
         <v>3.6057</v>
@@ -870,7 +870,7 @@
         <v>2.1137</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0274</v>
+        <v>0.9849</v>
       </c>
       <c r="E10" t="n">
         <v>3.5863</v>
@@ -916,7 +916,7 @@
         <v>1.8598</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8534</v>
+        <v>0.8132</v>
       </c>
       <c r="E11" t="n">
         <v>3.1555</v>
@@ -962,7 +962,7 @@
         <v>1.8418</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8411</v>
+        <v>0.8011</v>
       </c>
       <c r="E12" t="n">
         <v>3.1251</v>
@@ -1008,7 +1008,7 @@
         <v>1.7172</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7557</v>
+        <v>0.7169</v>
       </c>
       <c r="E13" t="n">
         <v>2.9136</v>
@@ -1054,7 +1054,7 @@
         <v>1.3776</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5229</v>
+        <v>0.4873</v>
       </c>
       <c r="E14" t="n">
         <v>2.3374</v>
@@ -1100,7 +1100,7 @@
         <v>1.2896</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4626</v>
+        <v>0.4278</v>
       </c>
       <c r="E15" t="n">
         <v>2.1881</v>
@@ -1146,7 +1146,7 @@
         <v>0.9465</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2274</v>
+        <v>0.1959</v>
       </c>
       <c r="E16" t="n">
         <v>1.6059</v>
@@ -1192,7 +1192,7 @@
         <v>0.8943</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1916</v>
+        <v>0.1606</v>
       </c>
       <c r="E17" t="n">
         <v>1.5174</v>
@@ -1238,7 +1238,7 @@
         <v>0.879</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1812</v>
+        <v>0.1503</v>
       </c>
       <c r="E18" t="n">
         <v>1.4915</v>
@@ -1284,7 +1284,7 @@
         <v>0.6155</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0278</v>
       </c>
       <c r="E19" t="n">
         <v>1.0444</v>
@@ -1330,7 +1330,7 @@
         <v>0.5819</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0225</v>
+        <v>-0.0506</v>
       </c>
       <c r="E20" t="n">
         <v>0.9873</v>
@@ -1376,7 +1376,7 @@
         <v>0.5227000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0631</v>
+        <v>-0.0906</v>
       </c>
       <c r="E21" t="n">
         <v>0.8869</v>
@@ -1422,7 +1422,7 @@
         <v>0.4681</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1005</v>
+        <v>-0.1275</v>
       </c>
       <c r="E22" t="n">
         <v>0.7942</v>
@@ -1468,7 +1468,7 @@
         <v>0.349</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1822</v>
+        <v>-0.208</v>
       </c>
       <c r="E23" t="n">
         <v>0.5921</v>
@@ -1514,7 +1514,7 @@
         <v>0.2511</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2492</v>
+        <v>-0.2742</v>
       </c>
       <c r="E24" t="n">
         <v>0.4261</v>
@@ -1560,7 +1560,7 @@
         <v>0.1739</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3021</v>
+        <v>-0.3263</v>
       </c>
       <c r="E25" t="n">
         <v>0.2951</v>
@@ -1606,7 +1606,7 @@
         <v>0.066</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3761</v>
+        <v>-0.3993</v>
       </c>
       <c r="E26" t="n">
         <v>0.112</v>
@@ -1652,7 +1652,7 @@
         <v>0.0496</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3873</v>
+        <v>-0.4104</v>
       </c>
       <c r="E27" t="n">
         <v>0.0842</v>
@@ -1698,7 +1698,7 @@
         <v>-0.063</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4645</v>
+        <v>-0.4865</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1069</v>
@@ -1744,7 +1744,7 @@
         <v>-0.3163</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6381</v>
+        <v>-0.6577</v>
       </c>
       <c r="E29" t="n">
         <v>-0.5366</v>
@@ -1790,7 +1790,7 @@
         <v>-0.4179</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7078</v>
+        <v>-0.7264</v>
       </c>
       <c r="E30" t="n">
         <v>-0.709</v>
@@ -1836,7 +1836,7 @@
         <v>-0.4193</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7088</v>
+        <v>-0.7274</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7115</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4341</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7189</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>-0.7366</v>
@@ -1928,7 +1928,7 @@
         <v>-0.7513</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9363</v>
+        <v>-0.9518</v>
       </c>
       <c r="E33" t="n">
         <v>-1.2747</v>
@@ -1974,7 +1974,7 @@
         <v>-0.7594</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9419</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="E34" t="n">
         <v>-1.2885</v>
@@ -2020,7 +2020,7 @@
         <v>-0.7794</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9556</v>
+        <v>-0.9708</v>
       </c>
       <c r="E35" t="n">
         <v>-1.3225</v>
@@ -2066,7 +2066,7 @@
         <v>-0.8428</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9991</v>
+        <v>-1.0136</v>
       </c>
       <c r="E36" t="n">
         <v>-1.43</v>
@@ -2112,7 +2112,7 @@
         <v>-0.8688</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0169</v>
+        <v>-1.0312</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4741</v>
@@ -2158,7 +2158,7 @@
         <v>-0.9787</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0922</v>
+        <v>-1.1055</v>
       </c>
       <c r="E38" t="n">
         <v>-1.6606</v>
@@ -2204,7 +2204,7 @@
         <v>-1.0635</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1503</v>
+        <v>-1.1628</v>
       </c>
       <c r="E39" t="n">
         <v>-1.8044</v>
@@ -2250,7 +2250,7 @@
         <v>-1.1248</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1924</v>
+        <v>-1.2043</v>
       </c>
       <c r="E40" t="n">
         <v>-1.9085</v>
@@ -2296,7 +2296,7 @@
         <v>-1.2979</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.311</v>
+        <v>-1.3213</v>
       </c>
       <c r="E41" t="n">
         <v>-2.2022</v>

--- a/database/event/1978/event_1978_evp_summary.xlsx
+++ b/database/event/1978/event_1978_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2577</v>
+        <v>6.9986</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2775</v>
+        <v>4.1248</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4476</v>
+        <v>2.5215</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2577</v>
+        <v>6.9986</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5118</v>
+        <v>4.4754</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7459</v>
+        <v>2.5232</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7714</v>
+        <v>6.4673</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7714</v>
+        <v>6.4673</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7459</v>
+        <v>2.5232</v>
       </c>
       <c r="K2" t="n">
         <v>313</v>
@@ -529,7 +529,7 @@
         <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>7.5173</v>
+        <v>8.990500000000001</v>
       </c>
       <c r="N2" t="n">
         <v>355</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4773</v>
+        <v>5.8463</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8175</v>
+        <v>3.4456</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1366</v>
+        <v>2.0013</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4773</v>
+        <v>5.8463</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7025</v>
+        <v>3.9995</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7748</v>
+        <v>1.8468</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0705</v>
+        <v>5.4224</v>
       </c>
       <c r="I3" t="n">
-        <v>5.0705</v>
+        <v>5.4224</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7748</v>
+        <v>1.8468</v>
       </c>
       <c r="K3" t="n">
         <v>313</v>
@@ -575,7 +575,7 @@
         <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8453</v>
+        <v>7.2692</v>
       </c>
       <c r="N3" t="n">
         <v>355</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4139</v>
+        <v>5.8011</v>
       </c>
       <c r="C4" t="n">
-        <v>3.7802</v>
+        <v>3.419</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1114</v>
+        <v>1.9809</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4139</v>
+        <v>5.8011</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7807</v>
+        <v>5.0737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6332</v>
+        <v>0.7274</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7611</v>
+        <v>7.7811</v>
       </c>
       <c r="I4" t="n">
-        <v>6.7611</v>
+        <v>7.7811</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6332</v>
+        <v>0.7274</v>
       </c>
       <c r="K4" t="n">
         <v>290</v>
@@ -621,7 +621,7 @@
         <v>42</v>
       </c>
       <c r="M4" t="n">
-        <v>7.394299999999999</v>
+        <v>8.5085</v>
       </c>
       <c r="N4" t="n">
         <v>332</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7433</v>
+        <v>5.357</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7956</v>
+        <v>3.1573</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4458</v>
+        <v>1.7804</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7433</v>
+        <v>5.357</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9357</v>
+        <v>3.0882</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8076</v>
+        <v>2.2688</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9357</v>
+        <v>3.4213</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9357</v>
+        <v>3.4213</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8076</v>
+        <v>2.2688</v>
       </c>
       <c r="K5" t="n">
         <v>313</v>
@@ -667,7 +667,7 @@
         <v>42</v>
       </c>
       <c r="M5" t="n">
-        <v>4.743300000000001</v>
+        <v>5.6901</v>
       </c>
       <c r="N5" t="n">
         <v>355</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1623</v>
+        <v>4.774</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4531</v>
+        <v>2.8137</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2144</v>
+        <v>1.5172</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1623</v>
+        <v>4.774</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5378</v>
+        <v>3.8345</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6245</v>
+        <v>0.9395</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5378</v>
+        <v>5.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5378</v>
+        <v>5.0601</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6245</v>
+        <v>0.9395</v>
       </c>
       <c r="K6" t="n">
         <v>313</v>
@@ -713,7 +713,7 @@
         <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1623</v>
+        <v>5.9996</v>
       </c>
       <c r="N6" t="n">
         <v>355</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0208</v>
+        <v>4.7332</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3697</v>
+        <v>2.7896</v>
       </c>
       <c r="D7" t="n">
-        <v>1.158</v>
+        <v>1.4988</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0208</v>
+        <v>4.7332</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9318</v>
+        <v>3.4105</v>
       </c>
       <c r="G7" t="n">
-        <v>1.089</v>
+        <v>1.3227</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9318</v>
+        <v>4.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9318</v>
+        <v>4.1291</v>
       </c>
       <c r="J7" t="n">
-        <v>1.089</v>
+        <v>1.3227</v>
       </c>
       <c r="K7" t="n">
         <v>313</v>
@@ -759,7 +759,7 @@
         <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>4.020799999999999</v>
+        <v>5.4518</v>
       </c>
       <c r="N7" t="n">
         <v>355</v>
@@ -768,32 +768,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8125</v>
+        <v>3.4857</v>
       </c>
       <c r="C8" t="n">
-        <v>2.247</v>
+        <v>2.0544</v>
       </c>
       <c r="D8" t="n">
-        <v>1.075</v>
+        <v>0.9356</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8125</v>
+        <v>3.4857</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8125</v>
+        <v>3.4857</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8125</v>
+        <v>4.2942</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8125</v>
+        <v>4.2942</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8125</v>
+        <v>4.2942</v>
       </c>
       <c r="N8" t="n">
         <v>178</v>
@@ -814,32 +814,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6057</v>
+        <v>3.3676</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1251</v>
+        <v>1.9848</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9926</v>
+        <v>0.8823</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6057</v>
+        <v>3.3676</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6057</v>
+        <v>3.3676</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6057</v>
+        <v>4.0349</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6057</v>
+        <v>4.0349</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6057</v>
+        <v>4.0349</v>
       </c>
       <c r="N9" t="n">
         <v>178</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5863</v>
+        <v>3.3245</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1137</v>
+        <v>1.9594</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9849</v>
+        <v>0.8628</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5863</v>
+        <v>3.3245</v>
       </c>
       <c r="F10" t="n">
-        <v>4.5863</v>
+        <v>3.2813</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>0.0432</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8882</v>
+        <v>3.8453</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8882</v>
+        <v>3.8453</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>0.0432</v>
       </c>
       <c r="K10" t="n">
         <v>290</v>
@@ -897,7 +897,7 @@
         <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8882</v>
+        <v>3.8885</v>
       </c>
       <c r="N10" t="n">
         <v>332</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1555</v>
+        <v>3.0312</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8598</v>
+        <v>1.7865</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8132</v>
+        <v>0.7304</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1555</v>
+        <v>3.0312</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1555</v>
+        <v>4.0025</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2129</v>
+        <v>5.4289</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2129</v>
+        <v>5.4289</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>290</v>
@@ -943,7 +943,7 @@
         <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2129</v>
+        <v>4.457599999999999</v>
       </c>
       <c r="N11" t="n">
         <v>332</v>
@@ -952,124 +952,124 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1251</v>
+        <v>2.9797</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8418</v>
+        <v>1.7561</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8011</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1251</v>
+        <v>2.9797</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4235</v>
+        <v>2.9797</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2984</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4235</v>
+        <v>3.1831</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4235</v>
+        <v>3.1831</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2984</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>290</v>
+        <v>155</v>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1251</v>
+        <v>3.1831</v>
       </c>
       <c r="N12" t="n">
-        <v>332</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9136</v>
+        <v>2.9629</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7172</v>
+        <v>1.7462</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7169</v>
+        <v>0.6996</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9136</v>
+        <v>2.9629</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9136</v>
+        <v>2.9629</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9136</v>
+        <v>3.1463</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9136</v>
+        <v>3.1463</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9136</v>
+        <v>3.1463</v>
       </c>
       <c r="N13" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3374</v>
+        <v>2.806</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3776</v>
+        <v>1.6538</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4873</v>
+        <v>0.6288</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3374</v>
+        <v>2.806</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3374</v>
+        <v>2.806</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3374</v>
+        <v>2.806</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3374</v>
+        <v>2.806</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3374</v>
+        <v>2.806</v>
       </c>
       <c r="N14" t="n">
         <v>155</v>
@@ -1090,78 +1090,78 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1881</v>
+        <v>2.6115</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2896</v>
+        <v>1.5391</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4278</v>
+        <v>0.5409</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1881</v>
+        <v>2.6115</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1881</v>
+        <v>2.6115</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1881</v>
+        <v>2.6115</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1881</v>
+        <v>2.6115</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1881</v>
+        <v>2.6115</v>
       </c>
       <c r="N15" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6059</v>
+        <v>2.6105</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9465</v>
+        <v>1.5385</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1959</v>
+        <v>0.5405</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6059</v>
+        <v>2.6105</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6059</v>
+        <v>3.6105</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6059</v>
+        <v>4.5683</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6059</v>
+        <v>4.5683</v>
       </c>
       <c r="J16" t="n">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6059</v>
+        <v>3.5683</v>
       </c>
       <c r="N16" t="n">
         <v>332</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5174</v>
+        <v>2.3505</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8943</v>
+        <v>1.3853</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1606</v>
+        <v>0.4231</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5174</v>
+        <v>2.3505</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5174</v>
+        <v>3.2921</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.9416</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5174</v>
+        <v>3.8692</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5174</v>
+        <v>3.8692</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.9416</v>
       </c>
       <c r="K17" t="n">
-        <v>155</v>
+        <v>290</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5174</v>
+        <v>2.9276</v>
       </c>
       <c r="N17" t="n">
-        <v>155</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4915</v>
+        <v>1.9253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.879</v>
+        <v>1.1347</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1503</v>
+        <v>0.2312</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4915</v>
+        <v>1.9253</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4915</v>
+        <v>1.9253</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4915</v>
+        <v>1.9253</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4915</v>
+        <v>1.9253</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4915</v>
+        <v>1.9253</v>
       </c>
       <c r="N18" t="n">
         <v>261</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0444</v>
+        <v>1.4216</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6155</v>
+        <v>0.8378</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0278</v>
+        <v>0.0038</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0444</v>
+        <v>1.4216</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0444</v>
+        <v>1.4216</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0444</v>
+        <v>1.4216</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0444</v>
+        <v>1.4216</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0444</v>
+        <v>1.4216</v>
       </c>
       <c r="N19" t="n">
         <v>261</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9873</v>
+        <v>1.349</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5819</v>
+        <v>0.7951</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0506</v>
+        <v>-0.029</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9873</v>
+        <v>1.349</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9873</v>
+        <v>1.349</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9873</v>
+        <v>1.349</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9873</v>
+        <v>1.349</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9873</v>
+        <v>1.349</v>
       </c>
       <c r="N20" t="n">
-        <v>178</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8869</v>
+        <v>1.3414</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.7906</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0906</v>
+        <v>-0.0324</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8869</v>
+        <v>1.3414</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8869</v>
+        <v>1.3414</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8869</v>
+        <v>1.3414</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8869</v>
+        <v>1.3414</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8869</v>
+        <v>1.3414</v>
       </c>
       <c r="N21" t="n">
         <v>261</v>
@@ -1412,277 +1412,277 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7942</v>
+        <v>1.2031</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4681</v>
+        <v>0.7091</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1275</v>
+        <v>-0.0949</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7942</v>
+        <v>1.2031</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7942</v>
+        <v>1.2031</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7942</v>
+        <v>1.2031</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7942</v>
+        <v>1.2031</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7942</v>
+        <v>1.2031</v>
       </c>
       <c r="N22" t="n">
-        <v>235</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5921</v>
+        <v>0.6675</v>
       </c>
       <c r="C23" t="n">
-        <v>0.349</v>
+        <v>0.3934</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.208</v>
+        <v>-0.3367</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5921</v>
+        <v>0.6675</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5921</v>
+        <v>0.6675</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5921</v>
+        <v>0.6675</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5921</v>
+        <v>0.6675</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5921</v>
+        <v>0.6675</v>
       </c>
       <c r="N23" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4261</v>
+        <v>0.6317</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2511</v>
+        <v>0.3723</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2742</v>
+        <v>-0.3528</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4261</v>
+        <v>0.6317</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4261</v>
+        <v>0.6317</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4261</v>
+        <v>0.6317</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4261</v>
+        <v>0.6317</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4261</v>
+        <v>0.6317</v>
       </c>
       <c r="N24" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2951</v>
+        <v>0.5437</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1739</v>
+        <v>0.3204</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3263</v>
+        <v>-0.3926</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2951</v>
+        <v>0.5437</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2951</v>
+        <v>0.5437</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2951</v>
+        <v>0.5437</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2951</v>
+        <v>0.5437</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>261</v>
+        <v>129</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2951</v>
+        <v>0.5437</v>
       </c>
       <c r="N25" t="n">
-        <v>261</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.112</v>
+        <v>0.502</v>
       </c>
       <c r="C26" t="n">
-        <v>0.066</v>
+        <v>0.2959</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3993</v>
+        <v>-0.4114</v>
       </c>
       <c r="E26" t="n">
-        <v>0.112</v>
+        <v>0.502</v>
       </c>
       <c r="F26" t="n">
-        <v>0.112</v>
+        <v>0.502</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.112</v>
+        <v>0.502</v>
       </c>
       <c r="I26" t="n">
-        <v>0.112</v>
+        <v>0.502</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.112</v>
+        <v>0.502</v>
       </c>
       <c r="N26" t="n">
-        <v>155</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0842</v>
+        <v>0.2748</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0496</v>
+        <v>0.162</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4104</v>
+        <v>-0.514</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0842</v>
+        <v>0.2748</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0842</v>
+        <v>0.2748</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0842</v>
+        <v>0.2748</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0842</v>
+        <v>0.2748</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0842</v>
+        <v>0.2748</v>
       </c>
       <c r="N27" t="n">
-        <v>235</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1069</v>
+        <v>0.1341</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.063</v>
+        <v>0.079</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4865</v>
+        <v>-0.5775</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1069</v>
+        <v>0.1341</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1069</v>
+        <v>0.1341</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1069</v>
+        <v>0.1341</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1069</v>
+        <v>0.1341</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1069</v>
+        <v>0.1341</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5366</v>
+        <v>-0.01</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3163</v>
+        <v>-0.0059</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6577</v>
+        <v>-0.6425</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5366</v>
+        <v>-0.01</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5366</v>
+        <v>-0.01</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5366</v>
+        <v>-0.01</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5366</v>
+        <v>-0.01</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5366</v>
+        <v>-0.01</v>
       </c>
       <c r="N29" t="n">
-        <v>129</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.709</v>
+        <v>-0.1914</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4179</v>
+        <v>-0.1128</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7264</v>
+        <v>-0.7244</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.709</v>
+        <v>-0.1914</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.709</v>
+        <v>-0.1914</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.709</v>
+        <v>-0.1914</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.709</v>
+        <v>-0.1914</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>235</v>
+        <v>129</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.709</v>
+        <v>-0.1914</v>
       </c>
       <c r="N30" t="n">
-        <v>235</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7115</v>
+        <v>-0.3552</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.4193</v>
+        <v>-0.2093</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7274</v>
+        <v>-0.7984</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7115</v>
+        <v>-0.3552</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7115</v>
+        <v>-0.3552</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7115</v>
+        <v>-0.3552</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7115</v>
+        <v>-0.3552</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7115</v>
+        <v>-0.3552</v>
       </c>
       <c r="N31" t="n">
         <v>123</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7366</v>
+        <v>-0.4369</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4341</v>
+        <v>-0.2575</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.8353</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7366</v>
+        <v>-0.4369</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7366</v>
+        <v>-0.4369</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7366</v>
+        <v>-0.4369</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7366</v>
+        <v>-0.4369</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7366</v>
+        <v>-0.4369</v>
       </c>
       <c r="N32" t="n">
         <v>123</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.2747</v>
+        <v>-0.6152</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.7513</v>
+        <v>-0.3626</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9518</v>
+        <v>-0.9157</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2747</v>
+        <v>-0.6152</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.2747</v>
+        <v>-0.6152</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.2747</v>
+        <v>-0.6152</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.2747</v>
+        <v>-0.6152</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.2747</v>
+        <v>-0.6152</v>
       </c>
       <c r="N33" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.2885</v>
+        <v>-0.704</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.7594</v>
+        <v>-0.4149</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.9558</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2885</v>
+        <v>-0.704</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.2885</v>
+        <v>-0.704</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.2885</v>
+        <v>-0.704</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.2885</v>
+        <v>-0.704</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2885</v>
+        <v>-0.704</v>
       </c>
       <c r="N34" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3225</v>
+        <v>-0.783</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.7794</v>
+        <v>-0.4615</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9708</v>
+        <v>-0.9915</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3225</v>
+        <v>-0.783</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3225</v>
+        <v>-0.783</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3225</v>
+        <v>-0.783</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3225</v>
+        <v>-0.783</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.3225</v>
+        <v>-0.783</v>
       </c>
       <c r="N35" t="n">
         <v>129</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.43</v>
+        <v>-0.9375</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.8428</v>
+        <v>-0.5525</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0136</v>
+        <v>-1.0612</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.43</v>
+        <v>-0.9375</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.43</v>
+        <v>-0.9375</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.43</v>
+        <v>-0.9375</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.43</v>
+        <v>-0.9375</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.43</v>
+        <v>-0.9375</v>
       </c>
       <c r="N36" t="n">
         <v>178</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4741</v>
+        <v>-1.1111</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.8688</v>
+        <v>-0.6548</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0312</v>
+        <v>-1.1396</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4741</v>
+        <v>-1.1111</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4741</v>
+        <v>-1.1111</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4741</v>
+        <v>-1.1111</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4741</v>
+        <v>-1.1111</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4741</v>
+        <v>-1.1111</v>
       </c>
       <c r="N37" t="n">
-        <v>235</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6606</v>
+        <v>-1.1761</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.9787</v>
+        <v>-0.6932</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1055</v>
+        <v>-1.169</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6606</v>
+        <v>-1.1761</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6606</v>
+        <v>-1.1761</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6606</v>
+        <v>-1.1761</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6606</v>
+        <v>-1.1761</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6606</v>
+        <v>-1.1761</v>
       </c>
       <c r="N38" t="n">
         <v>129</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8044</v>
+        <v>-1.2429</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.0635</v>
+        <v>-0.7325</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1628</v>
+        <v>-1.1991</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8044</v>
+        <v>-1.2429</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8044</v>
+        <v>-1.2429</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8044</v>
+        <v>-1.2429</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8044</v>
+        <v>-1.2429</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>235</v>
+        <v>129</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8044</v>
+        <v>-1.2429</v>
       </c>
       <c r="N39" t="n">
-        <v>235</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9085</v>
+        <v>-1.2957</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.1248</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2043</v>
+        <v>-1.223</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9085</v>
+        <v>-1.2957</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9085</v>
+        <v>-1.2957</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9085</v>
+        <v>-1.2957</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.9085</v>
+        <v>-1.2957</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9085</v>
+        <v>-1.2957</v>
       </c>
       <c r="N40" t="n">
         <v>155</v>
@@ -2286,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2022</v>
+        <v>-1.3337</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2979</v>
+        <v>-0.786</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3213</v>
+        <v>-1.2401</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2022</v>
+        <v>-1.3337</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2022</v>
+        <v>-1.3337</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2022</v>
+        <v>-1.3337</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2022</v>
+        <v>-1.3337</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2022</v>
+        <v>-1.3337</v>
       </c>
       <c r="N41" t="n">
-        <v>261</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3192</v>
+        <v>1.8681</v>
       </c>
       <c r="J2" t="n">
-        <v>44.0648</v>
+        <v>35.4939</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.69</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4243</v>
+        <v>1.3049</v>
       </c>
       <c r="J3" t="n">
-        <v>27.0617</v>
+        <v>24.7931</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7837</v>
+        <v>0.922</v>
       </c>
       <c r="J4" t="n">
-        <v>14.8903</v>
+        <v>17.518</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.29</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5715</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>10.8585</v>
+        <v>13.3209</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1174</v>
+        <v>-0.0308</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.2306</v>
+        <v>-0.5852000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4626</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>8.789400000000001</v>
+        <v>11.0409</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5513</v>
+        <v>-0.4032</v>
       </c>
       <c r="J8" t="n">
-        <v>-10.4747</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.4</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8023</v>
+        <v>-0.5523</v>
       </c>
       <c r="J9" t="n">
-        <v>-15.2437</v>
+        <v>-10.4937</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.36</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8556</v>
+        <v>-0.591</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.2564</v>
+        <v>-11.229</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.36</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8556</v>
+        <v>-0.591</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.2564</v>
+        <v>-11.229</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.59</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3216</v>
+        <v>1.2183</v>
       </c>
       <c r="J12" t="n">
-        <v>30.3968</v>
+        <v>28.0209</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2033</v>
+        <v>1.1457</v>
       </c>
       <c r="J13" t="n">
-        <v>27.6759</v>
+        <v>26.3511</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.925</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>21.275</v>
+        <v>22.3169</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3053</v>
+        <v>0.4007</v>
       </c>
       <c r="J15" t="n">
-        <v>7.0219</v>
+        <v>9.216100000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.15</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3053</v>
+        <v>0.4007</v>
       </c>
       <c r="J16" t="n">
-        <v>7.0219</v>
+        <v>9.216100000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.22</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5039</v>
+        <v>0.5955</v>
       </c>
       <c r="J17" t="n">
-        <v>11.5897</v>
+        <v>13.6965</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1706</v>
+        <v>0.1463</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9238</v>
+        <v>3.3649</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.62</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.57</v>
+        <v>-0.3803</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.11</v>
+        <v>-8.7469</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7269</v>
+        <v>-0.4922</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.7187</v>
+        <v>-11.3206</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.45</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7885</v>
+        <v>-0.5384</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.1355</v>
+        <v>-12.3832</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5382</v>
+        <v>0.6387</v>
       </c>
       <c r="J22" t="n">
-        <v>15.0696</v>
+        <v>17.8836</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0302</v>
+        <v>-0.0321</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8456</v>
+        <v>-0.8988</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.92</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1713</v>
+        <v>-0.1063</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.7964</v>
+        <v>-2.9764</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3095</v>
+        <v>-0.1922</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.666</v>
+        <v>-5.3816</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5101</v>
+        <v>-0.3302</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.2828</v>
+        <v>-9.2456</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.43</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0607</v>
+        <v>1.0425</v>
       </c>
       <c r="J27" t="n">
-        <v>29.6996</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8867</v>
+        <v>0.8968</v>
       </c>
       <c r="J28" t="n">
-        <v>24.8276</v>
+        <v>25.1104</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.438</v>
+        <v>0.5056</v>
       </c>
       <c r="J29" t="n">
-        <v>12.264</v>
+        <v>14.1568</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2479</v>
+        <v>0.3221</v>
       </c>
       <c r="J30" t="n">
-        <v>6.9412</v>
+        <v>9.018800000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.11</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2479</v>
+        <v>0.3221</v>
       </c>
       <c r="J31" t="n">
-        <v>6.9412</v>
+        <v>9.018800000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2089</v>
+        <v>-0.1827</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.3869</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.7</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3859</v>
+        <v>-0.2941</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.103899999999999</v>
+        <v>-6.1761</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.65</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4853</v>
+        <v>-0.3387</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.1913</v>
+        <v>-7.1127</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.534</v>
+        <v>-0.3661</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.214</v>
+        <v>-7.6881</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.58</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5937</v>
+        <v>-0.4032</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.4677</v>
+        <v>-8.4672</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.58</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2507</v>
+        <v>1.1896</v>
       </c>
       <c r="J37" t="n">
-        <v>26.2647</v>
+        <v>24.9816</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.55</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1896</v>
+        <v>1.1545</v>
       </c>
       <c r="J38" t="n">
-        <v>24.9816</v>
+        <v>24.2445</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.55</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1896</v>
+        <v>1.1545</v>
       </c>
       <c r="J39" t="n">
-        <v>24.9816</v>
+        <v>24.2445</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.44</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9295</v>
+        <v>1.0223</v>
       </c>
       <c r="J40" t="n">
-        <v>19.5195</v>
+        <v>21.4683</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.25</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5088</v>
+        <v>0.6254</v>
       </c>
       <c r="J41" t="n">
-        <v>10.6848</v>
+        <v>13.1334</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.78</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9236</v>
+        <v>0.8551</v>
       </c>
       <c r="J42" t="n">
-        <v>20.3192</v>
+        <v>18.8122</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.69</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8287</v>
+        <v>0.7678</v>
       </c>
       <c r="J43" t="n">
-        <v>18.2314</v>
+        <v>16.8916</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.45</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5322</v>
+        <v>0.5312</v>
       </c>
       <c r="J44" t="n">
-        <v>11.7084</v>
+        <v>11.6864</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.4</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4709</v>
+        <v>0.4786</v>
       </c>
       <c r="J45" t="n">
-        <v>10.3598</v>
+        <v>10.5292</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.29</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3351</v>
+        <v>0.3565</v>
       </c>
       <c r="J46" t="n">
-        <v>7.3722</v>
+        <v>7.843</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.92</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0391</v>
+        <v>-0.063</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8602</v>
+        <v>-1.386</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.87</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1253</v>
+        <v>-0.1233</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.7566</v>
+        <v>-2.7126</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.76</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3039</v>
+        <v>-0.2409</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.6858</v>
+        <v>-5.2998</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.4173</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.6048</v>
+        <v>-9.1806</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.38</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8619</v>
+        <v>-0.5948</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.9618</v>
+        <v>-13.0856</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.32</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6206</v>
+        <v>0.7591</v>
       </c>
       <c r="J52" t="n">
-        <v>14.2738</v>
+        <v>17.4593</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.83</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2446</v>
+        <v>-0.1868</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.6258</v>
+        <v>-4.2964</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2627</v>
+        <v>-0.1967</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.0421</v>
+        <v>-4.5241</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6599</v>
+        <v>-0.4422</v>
       </c>
       <c r="J55" t="n">
-        <v>-15.1777</v>
+        <v>-10.1706</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.48</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7593</v>
+        <v>-0.5161</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.4639</v>
+        <v>-11.8703</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.65</v>
       </c>
       <c r="I57" t="n">
-        <v>1.4447</v>
+        <v>1.2945</v>
       </c>
       <c r="J57" t="n">
-        <v>33.2281</v>
+        <v>29.7735</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.47</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0901</v>
+        <v>1.0754</v>
       </c>
       <c r="J58" t="n">
-        <v>25.0723</v>
+        <v>24.7342</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.38</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8912</v>
+        <v>0.9359</v>
       </c>
       <c r="J59" t="n">
-        <v>20.4976</v>
+        <v>21.5257</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.2</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4371</v>
+        <v>0.5321</v>
       </c>
       <c r="J60" t="n">
-        <v>10.0533</v>
+        <v>12.2383</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.02</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0693</v>
+        <v>0.0131</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.5939</v>
+        <v>0.3013</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.15</v>
       </c>
       <c r="I62" t="n">
-        <v>0.293</v>
+        <v>0.3334</v>
       </c>
       <c r="J62" t="n">
-        <v>8.789999999999999</v>
+        <v>10.002</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1544</v>
+        <v>0.1751</v>
       </c>
       <c r="J63" t="n">
-        <v>4.632</v>
+        <v>5.253</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.04</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0844</v>
+        <v>0.1099</v>
       </c>
       <c r="J64" t="n">
-        <v>2.532</v>
+        <v>3.297</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.06</v>
+        <v>0.0862</v>
       </c>
       <c r="J65" t="n">
-        <v>1.8</v>
+        <v>2.586</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1886</v>
+        <v>-0.1047</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.658</v>
+        <v>-3.141</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.71</v>
       </c>
       <c r="I67" t="n">
-        <v>1.6569</v>
+        <v>1.4291</v>
       </c>
       <c r="J67" t="n">
-        <v>49.707</v>
+        <v>42.873</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5246</v>
       </c>
       <c r="J68" t="n">
-        <v>16.014</v>
+        <v>15.738</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.09</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2467</v>
+        <v>0.29</v>
       </c>
       <c r="J69" t="n">
-        <v>7.401</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5085</v>
+        <v>-0.4425</v>
       </c>
       <c r="J70" t="n">
-        <v>-15.255</v>
+        <v>-13.275</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.79</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.6835</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.062</v>
+        <v>-20.505</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5842</v>
+        <v>1.4091</v>
       </c>
       <c r="J72" t="n">
-        <v>31.684</v>
+        <v>28.182</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.74</v>
       </c>
       <c r="I73" t="n">
-        <v>1.492</v>
+        <v>1.3538</v>
       </c>
       <c r="J73" t="n">
-        <v>29.84</v>
+        <v>27.076</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.71</v>
       </c>
       <c r="I74" t="n">
-        <v>1.4349</v>
+        <v>1.3205</v>
       </c>
       <c r="J74" t="n">
-        <v>28.698</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.56</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1095</v>
+        <v>1.1538</v>
       </c>
       <c r="J75" t="n">
-        <v>22.19</v>
+        <v>23.076</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.31</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5984</v>
+        <v>0.7353</v>
       </c>
       <c r="J76" t="n">
-        <v>11.968</v>
+        <v>14.706</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.6</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.4193</v>
+        <v>-0.3436</v>
       </c>
       <c r="J77" t="n">
-        <v>-8.385999999999999</v>
+        <v>-6.872</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.51</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5651</v>
+        <v>-0.4341</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.302</v>
+        <v>-8.682</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.47</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6531</v>
+        <v>-0.4691</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.062</v>
+        <v>-9.382</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.43</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.723</v>
+        <v>-0.5061</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.46</v>
+        <v>-10.122</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7698</v>
+        <v>-0.5349</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.396</v>
+        <v>-10.698</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.23</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4282</v>
+        <v>0.379</v>
       </c>
       <c r="J82" t="n">
-        <v>11.5614</v>
+        <v>10.233</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1381</v>
+        <v>0.1075</v>
       </c>
       <c r="J83" t="n">
-        <v>3.7287</v>
+        <v>2.9025</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1906</v>
+        <v>-0.111</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.1462</v>
+        <v>-2.997</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.91</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2085</v>
+        <v>-0.1224</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.6295</v>
+        <v>-3.3048</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.86</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2917</v>
+        <v>-0.1768</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.8759</v>
+        <v>-4.7736</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.61</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8577</v>
+        <v>0.7731</v>
       </c>
       <c r="J87" t="n">
-        <v>23.1579</v>
+        <v>20.8737</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.19</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3374</v>
+        <v>0.2821</v>
       </c>
       <c r="J88" t="n">
-        <v>9.1098</v>
+        <v>7.6167</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1448</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.9096</v>
+        <v>-1.9548</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.9</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.252</v>
+        <v>-0.1441</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.804</v>
+        <v>-3.8907</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4159</v>
+        <v>-0.2589</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.2293</v>
+        <v>-6.9903</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.22</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6414</v>
+        <v>0.6248</v>
       </c>
       <c r="J92" t="n">
-        <v>18.6006</v>
+        <v>18.1192</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.2</v>
       </c>
       <c r="I93" t="n">
-        <v>0.59</v>
+        <v>0.5755</v>
       </c>
       <c r="J93" t="n">
-        <v>17.11</v>
+        <v>16.6895</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.14</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4208</v>
+        <v>0.424</v>
       </c>
       <c r="J94" t="n">
-        <v>12.2032</v>
+        <v>12.296</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.14</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4208</v>
+        <v>0.424</v>
       </c>
       <c r="J95" t="n">
-        <v>12.2032</v>
+        <v>12.296</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3645</v>
+        <v>-0.2947</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.5705</v>
+        <v>-8.5463</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.99</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.0009</v>
+        <v>-0.0157</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.0261</v>
+        <v>-0.4553</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.98</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0271</v>
+        <v>-0.0314</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.7859</v>
+        <v>-0.9106</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.93</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1475</v>
+        <v>-0.0944</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.2775</v>
+        <v>-2.7376</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1682</v>
+        <v>-0.1058</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.8778</v>
+        <v>-3.0682</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.89</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2242</v>
+        <v>-0.1388</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.5018</v>
+        <v>-4.0252</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2862</v>
+        <v>0.2986</v>
       </c>
       <c r="J102" t="n">
-        <v>6.8688</v>
+        <v>7.1664</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.1216</v>
+        <v>-2.0184</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.88</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.181</v>
+        <v>-0.1407</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.344</v>
+        <v>-3.3768</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3354</v>
+        <v>-0.2205</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.0496</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.53</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7067</v>
+        <v>-0.476</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.9608</v>
+        <v>-11.424</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.52</v>
       </c>
       <c r="I107" t="n">
-        <v>1.209</v>
+        <v>1.143</v>
       </c>
       <c r="J107" t="n">
-        <v>29.016</v>
+        <v>27.432</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.209</v>
+        <v>1.143</v>
       </c>
       <c r="J108" t="n">
-        <v>29.016</v>
+        <v>27.432</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.18</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4014</v>
+        <v>0.4897</v>
       </c>
       <c r="J109" t="n">
-        <v>9.633599999999999</v>
+        <v>11.7528</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3761</v>
+        <v>0.4644</v>
       </c>
       <c r="J110" t="n">
-        <v>9.026400000000001</v>
+        <v>11.1456</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.16</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3505</v>
+        <v>0.4387</v>
       </c>
       <c r="J111" t="n">
-        <v>8.412000000000001</v>
+        <v>10.5288</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.85</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1052</v>
+        <v>-0.1124</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.8936</v>
+        <v>-2.0232</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.65</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4189</v>
+        <v>-0.3278</v>
       </c>
       <c r="J113" t="n">
-        <v>-7.5402</v>
+        <v>-5.9004</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5702</v>
+        <v>-0.3997</v>
       </c>
       <c r="J114" t="n">
-        <v>-10.2636</v>
+        <v>-7.1946</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.51</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6631</v>
+        <v>-0.4552</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.9358</v>
+        <v>-8.1936</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.41</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.55</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.4162</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.93</v>
       </c>
       <c r="I117" t="n">
-        <v>1.84</v>
+        <v>1.5677</v>
       </c>
       <c r="J117" t="n">
-        <v>33.12</v>
+        <v>28.2186</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.66</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3518</v>
+        <v>1.2678</v>
       </c>
       <c r="J118" t="n">
-        <v>24.3324</v>
+        <v>22.8204</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.57</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1472</v>
+        <v>1.1677</v>
       </c>
       <c r="J119" t="n">
-        <v>20.6496</v>
+        <v>21.0186</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.43</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8562</v>
+        <v>0.9917</v>
       </c>
       <c r="J120" t="n">
-        <v>15.4116</v>
+        <v>17.8506</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.37</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.8741</v>
       </c>
       <c r="J121" t="n">
-        <v>13.1832</v>
+        <v>15.7338</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.99</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0621</v>
+        <v>0.0184</v>
       </c>
       <c r="J122" t="n">
-        <v>1.6146</v>
+        <v>0.4784</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.92</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0834</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.1684</v>
+        <v>-2.2594</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1193</v>
+        <v>-0.1105</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.1018</v>
+        <v>-2.873</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.64</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.553</v>
+        <v>-0.3666</v>
       </c>
       <c r="J125" t="n">
-        <v>-14.378</v>
+        <v>-9.531599999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.53</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6965</v>
+        <v>-0.4692</v>
       </c>
       <c r="J126" t="n">
-        <v>-18.109</v>
+        <v>-12.1992</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.66</v>
       </c>
       <c r="I127" t="n">
-        <v>1.5146</v>
+        <v>1.3338</v>
       </c>
       <c r="J127" t="n">
-        <v>39.3796</v>
+        <v>34.6788</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.26</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6725</v>
+        <v>0.694</v>
       </c>
       <c r="J128" t="n">
-        <v>17.485</v>
+        <v>18.044</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6725</v>
+        <v>0.694</v>
       </c>
       <c r="J129" t="n">
-        <v>17.485</v>
+        <v>18.044</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5505</v>
+        <v>0.6028</v>
       </c>
       <c r="J130" t="n">
-        <v>14.313</v>
+        <v>15.6728</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8296</v>
+        <v>-0.784</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.5696</v>
+        <v>-20.384</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6227</v>
+        <v>0.5557</v>
       </c>
       <c r="J132" t="n">
-        <v>14.9448</v>
+        <v>13.3368</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.33</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4702</v>
+        <v>0.424</v>
       </c>
       <c r="J133" t="n">
-        <v>11.2848</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.31</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4423</v>
+        <v>0.4017</v>
       </c>
       <c r="J134" t="n">
-        <v>10.6152</v>
+        <v>9.6408</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.2</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2696</v>
+        <v>0.2751</v>
       </c>
       <c r="J135" t="n">
-        <v>6.4704</v>
+        <v>6.6024</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.08</v>
       </c>
       <c r="I136" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1142</v>
       </c>
       <c r="J136" t="n">
-        <v>2.028</v>
+        <v>2.7408</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.14</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3543</v>
+        <v>0.2965</v>
       </c>
       <c r="J137" t="n">
-        <v>8.5032</v>
+        <v>7.116</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2385</v>
+        <v>0.1809</v>
       </c>
       <c r="J138" t="n">
-        <v>5.724</v>
+        <v>4.3416</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1574</v>
+        <v>-0.1286</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.7776</v>
+        <v>-3.0864</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.55</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6801</v>
+        <v>-0.4564</v>
       </c>
       <c r="J140" t="n">
-        <v>-16.3224</v>
+        <v>-10.9536</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6925</v>
+        <v>-0.4656</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.62</v>
+        <v>-11.1744</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4947</v>
+        <v>0.578</v>
       </c>
       <c r="J142" t="n">
-        <v>11.3781</v>
+        <v>13.294</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1334</v>
+        <v>0.1066</v>
       </c>
       <c r="J143" t="n">
-        <v>3.0682</v>
+        <v>2.4518</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1082</v>
+        <v>-0.0963</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.4886</v>
+        <v>-2.2149</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.57</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6575</v>
+        <v>-0.4394</v>
       </c>
       <c r="J145" t="n">
-        <v>-15.1225</v>
+        <v>-10.1062</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.5037</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.0982</v>
+        <v>-11.5851</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0837</v>
+        <v>1.057</v>
       </c>
       <c r="J147" t="n">
-        <v>24.9251</v>
+        <v>24.311</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0204</v>
+        <v>1.0136</v>
       </c>
       <c r="J148" t="n">
-        <v>23.4692</v>
+        <v>23.3128</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5505</v>
+        <v>0.6028</v>
       </c>
       <c r="J149" t="n">
-        <v>12.6615</v>
+        <v>13.8644</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2214</v>
+        <v>0.295</v>
       </c>
       <c r="J150" t="n">
-        <v>5.0922</v>
+        <v>6.785</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.99</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1929</v>
+        <v>-0.1115</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.4367</v>
+        <v>-2.5645</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8354</v>
+        <v>0.8105</v>
       </c>
       <c r="J152" t="n">
-        <v>30.0744</v>
+        <v>29.178</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.26</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7653</v>
+        <v>0.7378</v>
       </c>
       <c r="J153" t="n">
-        <v>27.5508</v>
+        <v>26.5608</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6178</v>
+        <v>0.5889</v>
       </c>
       <c r="J154" t="n">
-        <v>22.2408</v>
+        <v>21.2004</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1839</v>
+        <v>0.2118</v>
       </c>
       <c r="J155" t="n">
-        <v>6.6204</v>
+        <v>7.6248</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.1424</v>
+        <v>-1.136</v>
       </c>
       <c r="J156" t="n">
-        <v>-41.1264</v>
+        <v>-40.896</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="J157" t="n">
-        <v>19.2528</v>
+        <v>23.004</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5089</v>
+        <v>0.6048</v>
       </c>
       <c r="J158" t="n">
-        <v>18.3204</v>
+        <v>21.7728</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.1</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2143</v>
+        <v>0.2386</v>
       </c>
       <c r="J159" t="n">
-        <v>7.7148</v>
+        <v>8.589600000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4053</v>
+        <v>-0.2529</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.5908</v>
+        <v>-9.1044</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.577</v>
+        <v>-0.3775</v>
       </c>
       <c r="J161" t="n">
-        <v>-20.772</v>
+        <v>-13.59</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.17</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>16.677</v>
+        <v>15.621</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.12</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4169</v>
+        <v>0.3872</v>
       </c>
       <c r="J163" t="n">
-        <v>12.507</v>
+        <v>11.616</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0522</v>
+        <v>0.0832</v>
       </c>
       <c r="J164" t="n">
-        <v>1.566</v>
+        <v>2.496</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0541</v>
+        <v>-0.0117</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.623</v>
+        <v>-0.351</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.97</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1983</v>
+        <v>-0.1442</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.949</v>
+        <v>-4.326</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6865</v>
+        <v>0.8446</v>
       </c>
       <c r="J167" t="n">
-        <v>20.595</v>
+        <v>25.338</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3903</v>
+        <v>0.4501</v>
       </c>
       <c r="J168" t="n">
-        <v>11.709</v>
+        <v>13.503</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.09</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2017</v>
+        <v>0.2208</v>
       </c>
       <c r="J169" t="n">
-        <v>6.051</v>
+        <v>6.624</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.75</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.458</v>
+        <v>-0.2908</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.74</v>
+        <v>-8.724</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.62</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6246</v>
+        <v>-0.4132</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.738</v>
+        <v>-12.396</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.58</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3503</v>
+        <v>1.2278</v>
       </c>
       <c r="J172" t="n">
-        <v>35.1078</v>
+        <v>31.9228</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.47</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1319</v>
+        <v>1.09</v>
       </c>
       <c r="J173" t="n">
-        <v>29.4294</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4508</v>
+        <v>0.5254</v>
       </c>
       <c r="J174" t="n">
-        <v>11.7208</v>
+        <v>13.6604</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.03</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.007</v>
+        <v>0.0698</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.182</v>
+        <v>1.8148</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.03</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.007</v>
+        <v>0.0698</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.182</v>
+        <v>1.8148</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.19</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4421</v>
+        <v>0.5063</v>
       </c>
       <c r="J177" t="n">
-        <v>11.4946</v>
+        <v>13.1638</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3033</v>
+        <v>0.319</v>
       </c>
       <c r="J178" t="n">
-        <v>7.8858</v>
+        <v>8.294</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.63</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.5694</v>
+        <v>-0.3775</v>
       </c>
       <c r="J179" t="n">
-        <v>-14.8044</v>
+        <v>-9.815</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.62</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5827</v>
+        <v>-0.3869</v>
       </c>
       <c r="J180" t="n">
-        <v>-15.1502</v>
+        <v>-10.0594</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.49</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7479</v>
+        <v>-0.5074</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.4454</v>
+        <v>-13.1924</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.31</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5089</v>
+        <v>0.4658</v>
       </c>
       <c r="J182" t="n">
-        <v>15.267</v>
+        <v>13.974</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4288</v>
+        <v>0.3872</v>
       </c>
       <c r="J183" t="n">
-        <v>12.864</v>
+        <v>11.616</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1099</v>
+        <v>0.1153</v>
       </c>
       <c r="J184" t="n">
-        <v>3.297</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0677</v>
+        <v>0.081</v>
       </c>
       <c r="J185" t="n">
-        <v>2.031</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.71</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.3347</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.591</v>
+        <v>-10.041</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.18</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3481</v>
+        <v>0.2822</v>
       </c>
       <c r="J187" t="n">
-        <v>10.443</v>
+        <v>8.465999999999999</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1853</v>
+        <v>0.1431</v>
       </c>
       <c r="J188" t="n">
-        <v>5.559</v>
+        <v>4.293</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.01</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0232</v>
+        <v>0.0256</v>
       </c>
       <c r="J189" t="n">
-        <v>0.696</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0505</v>
+        <v>-0.022</v>
       </c>
       <c r="J190" t="n">
-        <v>-1.515</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3439</v>
+        <v>-0.2107</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.317</v>
+        <v>-6.321</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6625</v>
+        <v>1.441</v>
       </c>
       <c r="J192" t="n">
-        <v>33.25</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2319</v>
+        <v>1.1719</v>
       </c>
       <c r="J193" t="n">
-        <v>24.638</v>
+        <v>23.438</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.47</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0427</v>
+        <v>1.0644</v>
       </c>
       <c r="J194" t="n">
-        <v>20.854</v>
+        <v>21.288</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.28</v>
       </c>
       <c r="I195" t="n">
-        <v>0.592</v>
+        <v>0.7044</v>
       </c>
       <c r="J195" t="n">
-        <v>11.84</v>
+        <v>14.088</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0112</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>0.224</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3357</v>
+        <v>0.3705</v>
       </c>
       <c r="J197" t="n">
-        <v>6.714</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.73</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3303</v>
+        <v>-0.2633</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.606</v>
+        <v>-5.266</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.67</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4323</v>
+        <v>-0.3201</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.646000000000001</v>
+        <v>-6.402</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.58</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5894</v>
+        <v>-0.4015</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.788</v>
+        <v>-8.029999999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.25</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.0097</v>
+        <v>-0.7117</v>
       </c>
       <c r="J201" t="n">
-        <v>-20.194</v>
+        <v>-14.234</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7714</v>
+        <v>0.7289</v>
       </c>
       <c r="J202" t="n">
-        <v>23.142</v>
+        <v>21.867</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.11</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4326</v>
+        <v>0.3812</v>
       </c>
       <c r="J203" t="n">
-        <v>12.978</v>
+        <v>11.436</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.99</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0541</v>
+        <v>-0.0519</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.623</v>
+        <v>-1.557</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.82</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6123</v>
+        <v>-0.5657</v>
       </c>
       <c r="J205" t="n">
-        <v>-18.369</v>
+        <v>-16.971</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.79</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6884</v>
+        <v>-0.644</v>
       </c>
       <c r="J206" t="n">
-        <v>-20.652</v>
+        <v>-19.32</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4704</v>
+        <v>0.5641</v>
       </c>
       <c r="J207" t="n">
-        <v>14.112</v>
+        <v>16.923</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.26</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4299</v>
+        <v>0.5133</v>
       </c>
       <c r="J208" t="n">
-        <v>12.897</v>
+        <v>15.399</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.06</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0929</v>
+        <v>0.145</v>
       </c>
       <c r="J209" t="n">
-        <v>2.787</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.03</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0322</v>
+        <v>0.0752</v>
       </c>
       <c r="J210" t="n">
-        <v>0.966</v>
+        <v>2.256</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.92</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2236</v>
+        <v>-0.1237</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.708</v>
+        <v>-3.711</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1085</v>
+        <v>1.0718</v>
       </c>
       <c r="J212" t="n">
-        <v>32.1465</v>
+        <v>31.0822</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.25</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6523</v>
+        <v>0.6725</v>
       </c>
       <c r="J213" t="n">
-        <v>18.9167</v>
+        <v>19.5025</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5957</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>17.2753</v>
+        <v>18.1685</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.18</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4454</v>
+        <v>0.508</v>
       </c>
       <c r="J215" t="n">
-        <v>12.9166</v>
+        <v>14.732</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.01</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.0736</v>
+        <v>0.0003</v>
       </c>
       <c r="J216" t="n">
-        <v>-2.1344</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.08</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2294</v>
+        <v>0.2321</v>
       </c>
       <c r="J217" t="n">
-        <v>6.6526</v>
+        <v>6.7309</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.05</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1741</v>
+        <v>0.164</v>
       </c>
       <c r="J218" t="n">
-        <v>5.0489</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0334</v>
+        <v>-0.0413</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.9686</v>
+        <v>-1.1977</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.88</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2254</v>
+        <v>-0.1458</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.5366</v>
+        <v>-4.2282</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.55</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6922</v>
+        <v>-0.4647</v>
       </c>
       <c r="J221" t="n">
-        <v>-20.0738</v>
+        <v>-13.4763</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.88</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.1033</v>
       </c>
       <c r="J222" t="n">
-        <v>-2.1781</v>
+        <v>-2.3759</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.75</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.3041</v>
+        <v>-0.2454</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.9943</v>
+        <v>-5.6442</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.62</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.534</v>
+        <v>-0.3661</v>
       </c>
       <c r="J224" t="n">
-        <v>-12.282</v>
+        <v>-8.420299999999999</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.608</v>
+        <v>-0.4125</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.984</v>
+        <v>-9.487500000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.65</v>
+        <v>-0.4406</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.95</v>
+        <v>-10.1338</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.71</v>
       </c>
       <c r="I227" t="n">
-        <v>1.5372</v>
+        <v>1.357</v>
       </c>
       <c r="J227" t="n">
-        <v>35.3556</v>
+        <v>31.211</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.58</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2921</v>
+        <v>1.2026</v>
       </c>
       <c r="J228" t="n">
-        <v>29.7183</v>
+        <v>27.6598</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.57</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2725</v>
+        <v>1.1906</v>
       </c>
       <c r="J229" t="n">
-        <v>29.2675</v>
+        <v>27.3838</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.22</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4692</v>
+        <v>0.572</v>
       </c>
       <c r="J230" t="n">
-        <v>10.7916</v>
+        <v>13.156</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6493</v>
+        <v>-0.584</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.9339</v>
+        <v>-13.432</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.08</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2007</v>
+        <v>0.2098</v>
       </c>
       <c r="J232" t="n">
-        <v>6.021</v>
+        <v>6.294</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0156</v>
+        <v>0.0025</v>
       </c>
       <c r="J233" t="n">
-        <v>0.468</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0216</v>
+        <v>-0.0194</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.648</v>
+        <v>-0.582</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0526</v>
+        <v>-0.0346</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.578</v>
+        <v>-1.038</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3035</v>
+        <v>-0.1856</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.105</v>
+        <v>-5.568</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8833</v>
+        <v>0.8601</v>
       </c>
       <c r="J237" t="n">
-        <v>26.499</v>
+        <v>25.803</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.16</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5148</v>
+        <v>0.4876</v>
       </c>
       <c r="J238" t="n">
-        <v>15.444</v>
+        <v>14.628</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.15</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4873</v>
+        <v>0.4614</v>
       </c>
       <c r="J239" t="n">
-        <v>14.619</v>
+        <v>13.842</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.02</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0369</v>
+        <v>0.0781</v>
       </c>
       <c r="J240" t="n">
-        <v>1.107</v>
+        <v>2.343</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8144</v>
+        <v>-0.7714</v>
       </c>
       <c r="J241" t="n">
-        <v>-24.432</v>
+        <v>-23.142</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3754</v>
+        <v>0.4163</v>
       </c>
       <c r="J242" t="n">
-        <v>9.009600000000001</v>
+        <v>9.991199999999999</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.89</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1704</v>
+        <v>-0.1316</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.0896</v>
+        <v>-3.1584</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.88</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1895</v>
+        <v>-0.1423</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.548</v>
+        <v>-3.4152</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.7</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4894</v>
+        <v>-0.3192</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.7456</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.68</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5168</v>
+        <v>-0.3382</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.4032</v>
+        <v>-8.1168</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>2.01</v>
       </c>
       <c r="I247" t="n">
-        <v>2.0241</v>
+        <v>1.7366</v>
       </c>
       <c r="J247" t="n">
-        <v>48.5784</v>
+        <v>41.6784</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5682</v>
+        <v>0.6414</v>
       </c>
       <c r="J248" t="n">
-        <v>13.6368</v>
+        <v>15.3936</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5682</v>
+        <v>0.6414</v>
       </c>
       <c r="J249" t="n">
-        <v>13.6368</v>
+        <v>15.3936</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.07</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1153</v>
+        <v>0.1957</v>
       </c>
       <c r="J250" t="n">
-        <v>2.7672</v>
+        <v>4.6968</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6523</v>
+        <v>-0.5886</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.6552</v>
+        <v>-14.1264</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.01</v>
       </c>
       <c r="I252" t="n">
-        <v>0.1414</v>
+        <v>0.1103</v>
       </c>
       <c r="J252" t="n">
-        <v>3.2522</v>
+        <v>2.5369</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.85</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1939</v>
+        <v>-0.1615</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.4597</v>
+        <v>-3.7145</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.76</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3607</v>
+        <v>-0.2501</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.296099999999999</v>
+        <v>-5.7523</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.64</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5455</v>
+        <v>-0.3631</v>
       </c>
       <c r="J255" t="n">
-        <v>-12.5465</v>
+        <v>-8.3513</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6001</v>
+        <v>-0.4006</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.8023</v>
+        <v>-9.213800000000001</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3114</v>
+        <v>1.2101</v>
       </c>
       <c r="J257" t="n">
-        <v>30.1622</v>
+        <v>27.8323</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.45</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0478</v>
+        <v>1.05</v>
       </c>
       <c r="J258" t="n">
-        <v>24.0994</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.42</v>
       </c>
       <c r="I259" t="n">
-        <v>0.9826</v>
+        <v>1.0071</v>
       </c>
       <c r="J259" t="n">
-        <v>22.5998</v>
+        <v>23.1633</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.29</v>
       </c>
       <c r="I260" t="n">
-        <v>0.6545</v>
+        <v>0.7441</v>
       </c>
       <c r="J260" t="n">
-        <v>15.0535</v>
+        <v>17.1143</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2664</v>
+        <v>-0.1788</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.1272</v>
+        <v>-4.1124</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.52</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6998</v>
+        <v>0.6279</v>
       </c>
       <c r="J262" t="n">
-        <v>15.3956</v>
+        <v>13.8138</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.45</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6175</v>
+        <v>0.553</v>
       </c>
       <c r="J263" t="n">
-        <v>13.585</v>
+        <v>12.166</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.24</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3223</v>
+        <v>0.3214</v>
       </c>
       <c r="J264" t="n">
-        <v>7.0906</v>
+        <v>7.0708</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.23</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3078</v>
+        <v>0.3096</v>
       </c>
       <c r="J265" t="n">
-        <v>6.7716</v>
+        <v>6.8112</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.02</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.0312</v>
+        <v>0.0126</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.6864</v>
+        <v>0.2772</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.97</v>
       </c>
       <c r="I267" t="n">
-        <v>0.005</v>
+        <v>-0.0264</v>
       </c>
       <c r="J267" t="n">
-        <v>0.11</v>
+        <v>-0.5808</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0934</v>
+        <v>-0.0911</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.0548</v>
+        <v>-2.0042</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.9</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1296</v>
+        <v>-0.1144</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.8512</v>
+        <v>-2.5168</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.71</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4615</v>
+        <v>-0.3035</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.153</v>
+        <v>-6.677</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6251</v>
+        <v>-0.4166</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.7522</v>
+        <v>-9.1652</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4372</v>
+        <v>0.5085</v>
       </c>
       <c r="J272" t="n">
-        <v>13.116</v>
+        <v>15.255</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.12</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2583</v>
+        <v>0.2845</v>
       </c>
       <c r="J273" t="n">
-        <v>7.749</v>
+        <v>8.535</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2074</v>
+        <v>0.224</v>
       </c>
       <c r="J274" t="n">
-        <v>6.222</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.88</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2637</v>
+        <v>-0.157</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.911</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.3276</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.258</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.23</v>
       </c>
       <c r="I277" t="n">
-        <v>0.675</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J277" t="n">
-        <v>20.25</v>
+        <v>19.611</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.17</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5191</v>
+        <v>0.5039</v>
       </c>
       <c r="J278" t="n">
-        <v>15.573</v>
+        <v>15.117</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.11</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3297</v>
+        <v>0.3483</v>
       </c>
       <c r="J279" t="n">
-        <v>9.891</v>
+        <v>10.449</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.09</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2606</v>
+        <v>0.2937</v>
       </c>
       <c r="J280" t="n">
-        <v>7.818</v>
+        <v>8.811</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.96</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.262</v>
+        <v>-0.1941</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.86</v>
+        <v>-5.823</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.05</v>
       </c>
       <c r="I282" t="n">
-        <v>0.1637</v>
+        <v>0.156</v>
       </c>
       <c r="J282" t="n">
-        <v>4.4199</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0459</v>
+        <v>-0.0445</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.2393</v>
+        <v>-1.2015</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0459</v>
+        <v>-0.0445</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.2393</v>
+        <v>-1.2015</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1129</v>
+        <v>-0.0824</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.0483</v>
+        <v>-2.2248</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.466</v>
+        <v>-0.2995</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.582</v>
+        <v>-8.086499999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.49</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2262</v>
+        <v>1.141</v>
       </c>
       <c r="J287" t="n">
-        <v>33.1074</v>
+        <v>30.807</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.29</v>
       </c>
       <c r="I288" t="n">
-        <v>0.796</v>
+        <v>0.7847</v>
       </c>
       <c r="J288" t="n">
-        <v>21.492</v>
+        <v>21.1869</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2629</v>
+        <v>0.3135</v>
       </c>
       <c r="J289" t="n">
-        <v>7.0983</v>
+        <v>8.464499999999999</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3116</v>
+        <v>-0.2381</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.4132</v>
+        <v>-6.4287</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.93</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3741</v>
+        <v>-0.3016</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.1007</v>
+        <v>-8.1432</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.28</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4886</v>
+        <v>0.5764</v>
       </c>
       <c r="J292" t="n">
-        <v>14.658</v>
+        <v>17.292</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.13</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2716</v>
+        <v>0.302</v>
       </c>
       <c r="J293" t="n">
-        <v>8.148</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.03</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0834</v>
+        <v>0.0893</v>
       </c>
       <c r="J294" t="n">
-        <v>2.502</v>
+        <v>2.679</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.89</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2495</v>
+        <v>-0.1471</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.485</v>
+        <v>-4.413</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.75</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4568</v>
+        <v>-0.2901</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.704</v>
+        <v>-8.702999999999999</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.18</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6044</v>
+        <v>0.5603</v>
       </c>
       <c r="J297" t="n">
-        <v>18.132</v>
+        <v>16.809</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.11</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4125</v>
+        <v>0.3705</v>
       </c>
       <c r="J298" t="n">
-        <v>12.375</v>
+        <v>11.115</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>0.038</v>
+        <v>0.0505</v>
       </c>
       <c r="J299" t="n">
-        <v>1.14</v>
+        <v>1.515</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0264</v>
+        <v>-0.0034</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.792</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6753</v>
+        <v>-0.6271</v>
       </c>
       <c r="J301" t="n">
-        <v>-20.259</v>
+        <v>-18.813</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.23</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4543</v>
+        <v>0.5244</v>
       </c>
       <c r="J302" t="n">
-        <v>11.3575</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.97</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.04</v>
+        <v>-0.0431</v>
       </c>
       <c r="J303" t="n">
-        <v>-1</v>
+        <v>-1.0775</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1952</v>
+        <v>-0.1258</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.88</v>
+        <v>-3.145</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.267</v>
+        <v>-0.1682</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.675</v>
+        <v>-4.205</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.64</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5826</v>
+        <v>-0.3833</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.565</v>
+        <v>-9.5825</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.88</v>
       </c>
       <c r="I307" t="n">
-        <v>1.9025</v>
+        <v>1.6038</v>
       </c>
       <c r="J307" t="n">
-        <v>47.5625</v>
+        <v>40.095</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.25</v>
       </c>
       <c r="I308" t="n">
-        <v>0.6538</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="J308" t="n">
-        <v>16.345</v>
+        <v>16.8225</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.21</v>
       </c>
       <c r="I309" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5809</v>
       </c>
       <c r="J309" t="n">
-        <v>13.2675</v>
+        <v>14.5225</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.98</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2312</v>
+        <v>-0.1502</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.78</v>
+        <v>-3.755</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.79</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7059</v>
       </c>
       <c r="J311" t="n">
-        <v>-18.965</v>
+        <v>-17.6475</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5542</v>
+        <v>0.6615</v>
       </c>
       <c r="J312" t="n">
-        <v>13.855</v>
+        <v>16.5375</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1392</v>
+        <v>0.1121</v>
       </c>
       <c r="J313" t="n">
-        <v>3.48</v>
+        <v>2.8025</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.74</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.4238</v>
+        <v>-0.2773</v>
       </c>
       <c r="J314" t="n">
-        <v>-10.595</v>
+        <v>-6.9325</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.7</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4817</v>
+        <v>-0.3156</v>
       </c>
       <c r="J315" t="n">
-        <v>-12.0425</v>
+        <v>-7.89</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.44</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.8125</v>
+        <v>-0.5567</v>
       </c>
       <c r="J316" t="n">
-        <v>-20.3125</v>
+        <v>-13.9175</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.59</v>
       </c>
       <c r="I317" t="n">
-        <v>1.379</v>
+        <v>1.2451</v>
       </c>
       <c r="J317" t="n">
-        <v>34.475</v>
+        <v>31.1275</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.38</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9513</v>
+        <v>0.9585</v>
       </c>
       <c r="J318" t="n">
-        <v>23.7825</v>
+        <v>23.9625</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.18</v>
       </c>
       <c r="I319" t="n">
-        <v>0.4357</v>
+        <v>0.5048</v>
       </c>
       <c r="J319" t="n">
-        <v>10.8925</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.08</v>
       </c>
       <c r="I320" t="n">
-        <v>0.16</v>
+        <v>0.2352</v>
       </c>
       <c r="J320" t="n">
-        <v>4</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.97</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2741</v>
+        <v>-0.1919</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.8525</v>
+        <v>-4.7975</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.92</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.0762</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J322" t="n">
-        <v>-1.7526</v>
+        <v>-1.9228</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.85</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1979</v>
+        <v>-0.1629</v>
       </c>
       <c r="J323" t="n">
-        <v>-4.5517</v>
+        <v>-3.7467</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.73</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.416</v>
+        <v>-0.2793</v>
       </c>
       <c r="J324" t="n">
-        <v>-9.568</v>
+        <v>-6.4239</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.416</v>
+        <v>-0.2793</v>
       </c>
       <c r="J325" t="n">
-        <v>-9.568</v>
+        <v>-6.4239</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5059</v>
+        <v>-0.336</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.6357</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.76</v>
       </c>
       <c r="I327" t="n">
-        <v>1.6362</v>
+        <v>1.4201</v>
       </c>
       <c r="J327" t="n">
-        <v>37.6326</v>
+        <v>32.6623</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.52</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1822</v>
+        <v>1.1333</v>
       </c>
       <c r="J328" t="n">
-        <v>27.1906</v>
+        <v>26.0659</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.46</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0575</v>
+        <v>1.0597</v>
       </c>
       <c r="J329" t="n">
-        <v>24.3225</v>
+        <v>24.3731</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.33</v>
       </c>
       <c r="I330" t="n">
-        <v>0.7382</v>
+        <v>0.8288</v>
       </c>
       <c r="J330" t="n">
-        <v>16.9786</v>
+        <v>19.0624</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.76</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8546</v>
+        <v>-0.8113</v>
       </c>
       <c r="J331" t="n">
-        <v>-19.6558</v>
+        <v>-18.6599</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.79</v>
       </c>
       <c r="I332" t="n">
-        <v>1.637</v>
+        <v>1.4291</v>
       </c>
       <c r="J332" t="n">
-        <v>34.377</v>
+        <v>30.0111</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.69</v>
       </c>
       <c r="I333" t="n">
-        <v>1.455</v>
+        <v>1.3147</v>
       </c>
       <c r="J333" t="n">
-        <v>30.555</v>
+        <v>27.6087</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.5</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0675</v>
+        <v>1.0945</v>
       </c>
       <c r="J334" t="n">
-        <v>22.4175</v>
+        <v>22.9845</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.5</v>
       </c>
       <c r="I335" t="n">
-        <v>1.0675</v>
+        <v>1.0945</v>
       </c>
       <c r="J335" t="n">
-        <v>22.4175</v>
+        <v>22.9845</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.98</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2989</v>
+        <v>-0.2092</v>
       </c>
       <c r="J336" t="n">
-        <v>-6.2769</v>
+        <v>-4.3932</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.82</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1397</v>
+        <v>-0.1378</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.9337</v>
+        <v>-2.8938</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.3411</v>
+        <v>-0.2815</v>
       </c>
       <c r="J338" t="n">
-        <v>-7.1631</v>
+        <v>-5.9115</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.59</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.5029</v>
+        <v>-0.3791</v>
       </c>
       <c r="J339" t="n">
-        <v>-10.5609</v>
+        <v>-7.9611</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.43</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.7663</v>
+        <v>-0.5262</v>
       </c>
       <c r="J340" t="n">
-        <v>-16.0923</v>
+        <v>-11.0502</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.34</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.8851</v>
+        <v>-0.6131</v>
       </c>
       <c r="J341" t="n">
-        <v>-18.5871</v>
+        <v>-12.8751</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.351</v>
+        <v>1.2257</v>
       </c>
       <c r="J342" t="n">
-        <v>31.073</v>
+        <v>28.1911</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.35</v>
       </c>
       <c r="I343" t="n">
-        <v>0.8966</v>
+        <v>0.9019</v>
       </c>
       <c r="J343" t="n">
-        <v>20.6218</v>
+        <v>20.7437</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.29</v>
       </c>
       <c r="I344" t="n">
-        <v>0.7573</v>
+        <v>0.7659</v>
       </c>
       <c r="J344" t="n">
-        <v>17.4179</v>
+        <v>17.6157</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.99</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1881</v>
+        <v>-0.1081</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.3263</v>
+        <v>-2.4863</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.89</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.4367</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.6978</v>
+        <v>-10.0441</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.98</v>
       </c>
       <c r="I347" t="n">
-        <v>0.0182</v>
+        <v>-0.0159</v>
       </c>
       <c r="J347" t="n">
-        <v>0.4186</v>
+        <v>-0.3657</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.98</v>
       </c>
       <c r="I348" t="n">
-        <v>0.0182</v>
+        <v>-0.0159</v>
       </c>
       <c r="J348" t="n">
-        <v>0.4186</v>
+        <v>-0.3657</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.92</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1035</v>
+        <v>-0.0948</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.3805</v>
+        <v>-2.1804</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.497</v>
+        <v>-0.3257</v>
       </c>
       <c r="J350" t="n">
-        <v>-11.431</v>
+        <v>-7.4911</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.63</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5782</v>
+        <v>-0.3823</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.2986</v>
+        <v>-8.792899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1978/event_1978_evp_summary.xlsx
+++ b/database/event/1978/event_1978_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9986</v>
+        <v>6.7825</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1248</v>
+        <v>3.9974</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5215</v>
+        <v>2.4633</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9986</v>
+        <v>6.7825</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4754</v>
+        <v>4.1293</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5232</v>
+        <v>2.6532</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4673</v>
+        <v>6.3128</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4673</v>
+        <v>6.3128</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5232</v>
+        <v>2.6532</v>
       </c>
       <c r="K2" t="n">
         <v>313</v>
@@ -529,7 +529,7 @@
         <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>8.990500000000001</v>
+        <v>8.966000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>355</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8463</v>
+        <v>5.4911</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4456</v>
+        <v>3.2363</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0013</v>
+        <v>1.8755</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8463</v>
+        <v>5.4911</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9995</v>
+        <v>3.6516</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8468</v>
+        <v>1.8395</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4224</v>
+        <v>5.2673</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4224</v>
+        <v>5.2673</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8468</v>
+        <v>1.8395</v>
       </c>
       <c r="K3" t="n">
         <v>313</v>
@@ -575,7 +575,7 @@
         <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>7.2692</v>
+        <v>7.1068</v>
       </c>
       <c r="N3" t="n">
         <v>355</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8011</v>
+        <v>5.3231</v>
       </c>
       <c r="C4" t="n">
-        <v>3.419</v>
+        <v>3.1373</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9809</v>
+        <v>1.799</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8011</v>
+        <v>5.3231</v>
       </c>
       <c r="F4" t="n">
-        <v>5.0737</v>
+        <v>4.6816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7274</v>
+        <v>0.6415</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7811</v>
+        <v>7.5217</v>
       </c>
       <c r="I4" t="n">
-        <v>7.7811</v>
+        <v>7.5217</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7274</v>
+        <v>0.6415</v>
       </c>
       <c r="K4" t="n">
         <v>290</v>
@@ -621,7 +621,7 @@
         <v>42</v>
       </c>
       <c r="M4" t="n">
-        <v>8.5085</v>
+        <v>8.1632</v>
       </c>
       <c r="N4" t="n">
         <v>332</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.357</v>
+        <v>5.0231</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1573</v>
+        <v>2.9605</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7804</v>
+        <v>1.6624</v>
       </c>
       <c r="E5" t="n">
-        <v>5.357</v>
+        <v>5.0231</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0882</v>
+        <v>2.7694</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2688</v>
+        <v>2.2537</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4213</v>
+        <v>3.3364</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4213</v>
+        <v>3.3364</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2688</v>
+        <v>2.2537</v>
       </c>
       <c r="K5" t="n">
         <v>313</v>
@@ -667,7 +667,7 @@
         <v>42</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6901</v>
+        <v>5.5901</v>
       </c>
       <c r="N5" t="n">
         <v>355</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.774</v>
+        <v>4.418</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8137</v>
+        <v>2.6038</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5172</v>
+        <v>1.387</v>
       </c>
       <c r="E6" t="n">
-        <v>4.774</v>
+        <v>4.418</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8345</v>
+        <v>3.4851</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9395</v>
+        <v>0.9329</v>
       </c>
       <c r="H6" t="n">
-        <v>5.0601</v>
+        <v>4.9029</v>
       </c>
       <c r="I6" t="n">
-        <v>5.0601</v>
+        <v>4.9029</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9395</v>
+        <v>0.9329</v>
       </c>
       <c r="K6" t="n">
         <v>313</v>
@@ -713,7 +713,7 @@
         <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>5.9996</v>
+        <v>5.8358</v>
       </c>
       <c r="N6" t="n">
         <v>355</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7332</v>
+        <v>4.344</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7896</v>
+        <v>2.5602</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4988</v>
+        <v>1.3533</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7332</v>
+        <v>4.344</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4105</v>
+        <v>3.056</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3227</v>
+        <v>1.288</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1291</v>
+        <v>3.9638</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1291</v>
+        <v>3.9638</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3227</v>
+        <v>1.288</v>
       </c>
       <c r="K7" t="n">
         <v>313</v>
@@ -759,7 +759,7 @@
         <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>5.4518</v>
+        <v>5.2518</v>
       </c>
       <c r="N7" t="n">
         <v>355</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4857</v>
+        <v>3.175</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0544</v>
+        <v>1.8712</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9356</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4857</v>
+        <v>3.175</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4857</v>
+        <v>3.175</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2942</v>
+        <v>4.2242</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2942</v>
+        <v>4.2242</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2942</v>
+        <v>4.2242</v>
       </c>
       <c r="N8" t="n">
         <v>178</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3676</v>
+        <v>3.0359</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9848</v>
+        <v>1.7893</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8823</v>
+        <v>0.7578</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3676</v>
+        <v>3.0359</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3676</v>
+        <v>3.0359</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0349</v>
+        <v>3.9196</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0349</v>
+        <v>3.9196</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0349</v>
+        <v>3.9196</v>
       </c>
       <c r="N9" t="n">
         <v>178</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3245</v>
+        <v>2.9508</v>
       </c>
       <c r="C10" t="n">
-        <v>1.9594</v>
+        <v>1.7391</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8628</v>
+        <v>0.7191</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3245</v>
+        <v>2.9508</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2813</v>
+        <v>2.9566</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0432</v>
+        <v>-0.0058</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8453</v>
+        <v>3.7462</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8453</v>
+        <v>3.7462</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0432</v>
+        <v>-0.0058</v>
       </c>
       <c r="K10" t="n">
         <v>290</v>
@@ -897,7 +897,7 @@
         <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8885</v>
+        <v>3.7404</v>
       </c>
       <c r="N10" t="n">
         <v>332</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0312</v>
+        <v>2.6887</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7865</v>
+        <v>1.5846</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7304</v>
+        <v>0.5997</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0312</v>
+        <v>2.6887</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0025</v>
+        <v>3.6823</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.9936</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4289</v>
+        <v>5.3345</v>
       </c>
       <c r="I11" t="n">
-        <v>5.4289</v>
+        <v>5.3345</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.9936</v>
       </c>
       <c r="K11" t="n">
         <v>290</v>
@@ -943,7 +943,7 @@
         <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>4.457599999999999</v>
+        <v>4.3409</v>
       </c>
       <c r="N11" t="n">
         <v>332</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9797</v>
+        <v>2.6527</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7561</v>
+        <v>1.5634</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.5834</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9797</v>
+        <v>2.6527</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9797</v>
+        <v>2.6527</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1831</v>
+        <v>3.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1831</v>
+        <v>3.0809</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1831</v>
+        <v>3.0809</v>
       </c>
       <c r="N12" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9629</v>
+        <v>2.6305</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7462</v>
+        <v>1.5503</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6996</v>
+        <v>0.5733</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9629</v>
+        <v>2.6305</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9629</v>
+        <v>2.6305</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1463</v>
+        <v>3.0324</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1463</v>
+        <v>3.0324</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1463</v>
+        <v>3.0324</v>
       </c>
       <c r="N13" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.806</v>
+        <v>2.4743</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6538</v>
+        <v>1.4583</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6288</v>
+        <v>0.5021</v>
       </c>
       <c r="E14" t="n">
-        <v>2.806</v>
+        <v>2.4743</v>
       </c>
       <c r="F14" t="n">
-        <v>2.806</v>
+        <v>2.4743</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.806</v>
+        <v>2.6905</v>
       </c>
       <c r="I14" t="n">
-        <v>2.806</v>
+        <v>2.6905</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.806</v>
+        <v>2.6905</v>
       </c>
       <c r="N14" t="n">
         <v>155</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6115</v>
+        <v>2.3669</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5391</v>
+        <v>1.395</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5409</v>
+        <v>0.4533</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6115</v>
+        <v>2.3669</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6115</v>
+        <v>2.3669</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6115</v>
+        <v>2.4555</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6115</v>
+        <v>2.4555</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6115</v>
+        <v>2.4555</v>
       </c>
       <c r="N15" t="n">
         <v>155</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6105</v>
+        <v>2.2653</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5385</v>
+        <v>1.3351</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5405</v>
+        <v>0.407</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6105</v>
+        <v>2.2653</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6105</v>
+        <v>3.2653</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5683</v>
+        <v>4.4218</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5683</v>
+        <v>4.4218</v>
       </c>
       <c r="J16" t="n">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5683</v>
+        <v>3.4218</v>
       </c>
       <c r="N16" t="n">
         <v>332</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3505</v>
+        <v>2.0396</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3853</v>
+        <v>1.2021</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4231</v>
+        <v>0.3043</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3505</v>
+        <v>2.0396</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2921</v>
+        <v>3.0074</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9416</v>
+        <v>-0.9678</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8692</v>
+        <v>3.8573</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8692</v>
+        <v>3.8573</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9416</v>
+        <v>-0.9678</v>
       </c>
       <c r="K17" t="n">
         <v>290</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9276</v>
+        <v>2.8895</v>
       </c>
       <c r="N17" t="n">
         <v>332</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9253</v>
+        <v>1.8291</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1347</v>
+        <v>1.078</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2312</v>
+        <v>0.2084</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9253</v>
+        <v>1.8291</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9253</v>
+        <v>1.8291</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9253</v>
+        <v>1.8291</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9253</v>
+        <v>1.8291</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9253</v>
+        <v>1.8291</v>
       </c>
       <c r="N18" t="n">
         <v>261</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4216</v>
+        <v>1.3776</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8378</v>
+        <v>0.8119</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0038</v>
+        <v>0.0029</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4216</v>
+        <v>1.3776</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4216</v>
+        <v>1.3776</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4216</v>
+        <v>1.3776</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4216</v>
+        <v>1.3776</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4216</v>
+        <v>1.3776</v>
       </c>
       <c r="N19" t="n">
         <v>261</v>
@@ -1320,231 +1320,231 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.349</v>
+        <v>1.2355</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7951</v>
+        <v>0.7282</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.029</v>
+        <v>-0.0618</v>
       </c>
       <c r="E20" t="n">
-        <v>1.349</v>
+        <v>1.2355</v>
       </c>
       <c r="F20" t="n">
-        <v>1.349</v>
+        <v>1.2355</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.349</v>
+        <v>1.2355</v>
       </c>
       <c r="I20" t="n">
-        <v>1.349</v>
+        <v>1.2355</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.349</v>
+        <v>1.2355</v>
       </c>
       <c r="N20" t="n">
-        <v>235</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3414</v>
+        <v>1.202</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7906</v>
+        <v>0.7084</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0324</v>
+        <v>-0.077</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3414</v>
+        <v>1.202</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3414</v>
+        <v>1.202</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3414</v>
+        <v>1.202</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3414</v>
+        <v>1.202</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>261</v>
+        <v>178</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3414</v>
+        <v>1.202</v>
       </c>
       <c r="N21" t="n">
-        <v>261</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2031</v>
+        <v>1.196</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7091</v>
+        <v>0.7049</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0949</v>
+        <v>-0.0798</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2031</v>
+        <v>1.196</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2031</v>
+        <v>1.196</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2031</v>
+        <v>1.196</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2031</v>
+        <v>1.196</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2031</v>
+        <v>1.196</v>
       </c>
       <c r="N22" t="n">
-        <v>178</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6675</v>
+        <v>0.5878</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3934</v>
+        <v>0.3464</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3367</v>
+        <v>-0.3566</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6675</v>
+        <v>0.5878</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6675</v>
+        <v>0.5878</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6675</v>
+        <v>0.5878</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6675</v>
+        <v>0.5878</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>235</v>
+        <v>123</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6675</v>
+        <v>0.5878</v>
       </c>
       <c r="N23" t="n">
-        <v>235</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6317</v>
+        <v>0.5375</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3723</v>
+        <v>0.3168</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3528</v>
+        <v>-0.3795</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6317</v>
+        <v>0.5375</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6317</v>
+        <v>0.5375</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6317</v>
+        <v>0.5375</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6317</v>
+        <v>0.5375</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6317</v>
+        <v>0.5375</v>
       </c>
       <c r="N24" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5437</v>
+        <v>0.4678</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3204</v>
+        <v>0.2757</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3926</v>
+        <v>-0.4113</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5437</v>
+        <v>0.4678</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5437</v>
+        <v>0.4678</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5437</v>
+        <v>0.4678</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5437</v>
+        <v>0.4678</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5437</v>
+        <v>0.4678</v>
       </c>
       <c r="N25" t="n">
         <v>129</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.502</v>
+        <v>0.4453</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2959</v>
+        <v>0.2624</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4114</v>
+        <v>-0.4215</v>
       </c>
       <c r="E26" t="n">
-        <v>0.502</v>
+        <v>0.4453</v>
       </c>
       <c r="F26" t="n">
-        <v>0.502</v>
+        <v>0.4453</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.502</v>
+        <v>0.4453</v>
       </c>
       <c r="I26" t="n">
-        <v>0.502</v>
+        <v>0.4453</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.502</v>
+        <v>0.4453</v>
       </c>
       <c r="N26" t="n">
         <v>261</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2748</v>
+        <v>0.2733</v>
       </c>
       <c r="C27" t="n">
-        <v>0.162</v>
+        <v>0.1611</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.514</v>
+        <v>-0.4998</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2748</v>
+        <v>0.2733</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2748</v>
+        <v>0.2733</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2748</v>
+        <v>0.2733</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2748</v>
+        <v>0.2733</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2748</v>
+        <v>0.2733</v>
       </c>
       <c r="N27" t="n">
         <v>155</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1341</v>
+        <v>0.108</v>
       </c>
       <c r="C28" t="n">
-        <v>0.079</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5775</v>
+        <v>-0.575</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1341</v>
+        <v>0.108</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1341</v>
+        <v>0.108</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1341</v>
+        <v>0.108</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1341</v>
+        <v>0.108</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1341</v>
+        <v>0.108</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01</v>
+        <v>-0.1691</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0059</v>
+        <v>-0.0997</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6425</v>
+        <v>-0.7012</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.01</v>
+        <v>-0.1691</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01</v>
+        <v>-0.1691</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.01</v>
+        <v>-0.1691</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01</v>
+        <v>-0.1691</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.01</v>
+        <v>-0.1691</v>
       </c>
       <c r="N29" t="n">
         <v>235</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1914</v>
+        <v>-0.2538</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1128</v>
+        <v>-0.1496</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7244</v>
+        <v>-0.7397</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1914</v>
+        <v>-0.2538</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1914</v>
+        <v>-0.2538</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1914</v>
+        <v>-0.2538</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1914</v>
+        <v>-0.2538</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1914</v>
+        <v>-0.2538</v>
       </c>
       <c r="N30" t="n">
         <v>129</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3552</v>
+        <v>-0.3843</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2093</v>
+        <v>-0.2265</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7984</v>
+        <v>-0.7991</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3552</v>
+        <v>-0.3843</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3552</v>
+        <v>-0.3843</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3552</v>
+        <v>-0.3843</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3552</v>
+        <v>-0.3843</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3552</v>
+        <v>-0.3843</v>
       </c>
       <c r="N31" t="n">
         <v>123</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4369</v>
+        <v>-0.4392</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2575</v>
+        <v>-0.2589</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8353</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4369</v>
+        <v>-0.4392</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4369</v>
+        <v>-0.4392</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4369</v>
+        <v>-0.4392</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4369</v>
+        <v>-0.4392</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4369</v>
+        <v>-0.4392</v>
       </c>
       <c r="N32" t="n">
         <v>123</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6152</v>
+        <v>-0.7164</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3626</v>
+        <v>-0.4222</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9157</v>
+        <v>-0.9503</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6152</v>
+        <v>-0.7164</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6152</v>
+        <v>-0.7164</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6152</v>
+        <v>-0.7164</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6152</v>
+        <v>-0.7164</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6152</v>
+        <v>-0.7164</v>
       </c>
       <c r="N33" t="n">
         <v>235</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.704</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4149</v>
+        <v>-0.4489</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9558</v>
+        <v>-0.9709</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.704</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.704</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.704</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.704</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.704</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>123</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.783</v>
+        <v>-0.8082</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4615</v>
+        <v>-0.4763</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9915</v>
+        <v>-0.9921</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.783</v>
+        <v>-0.8082</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.783</v>
+        <v>-0.8082</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.783</v>
+        <v>-0.8082</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.783</v>
+        <v>-0.8082</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.783</v>
+        <v>-0.8082</v>
       </c>
       <c r="N35" t="n">
         <v>129</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9375</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5525</v>
+        <v>-0.478</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0612</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9375</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9375</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9375</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9375</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9375</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>178</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1111</v>
+        <v>-1.1263</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6548</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1396</v>
+        <v>-1.1369</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1111</v>
+        <v>-1.1263</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1111</v>
+        <v>-1.1263</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1111</v>
+        <v>-1.1263</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1111</v>
+        <v>-1.1263</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1111</v>
+        <v>-1.1263</v>
       </c>
       <c r="N37" t="n">
         <v>261</v>
@@ -2148,78 +2148,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1761</v>
+        <v>-1.2309</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6932</v>
+        <v>-0.7255</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.169</v>
+        <v>-1.1845</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1761</v>
+        <v>-1.2309</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1761</v>
+        <v>-1.2309</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1761</v>
+        <v>-1.2309</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1761</v>
+        <v>-1.2309</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1761</v>
+        <v>-1.2309</v>
       </c>
       <c r="N38" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2429</v>
+        <v>-1.238</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7325</v>
+        <v>-0.7296</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1991</v>
+        <v>-1.1878</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2429</v>
+        <v>-1.238</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2429</v>
+        <v>-1.238</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2429</v>
+        <v>-1.238</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2429</v>
+        <v>-1.238</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2429</v>
+        <v>-1.238</v>
       </c>
       <c r="N39" t="n">
         <v>129</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2957</v>
+        <v>-1.266</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7461</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.223</v>
+        <v>-1.2005</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2957</v>
+        <v>-1.266</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2957</v>
+        <v>-1.266</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2957</v>
+        <v>-1.266</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2957</v>
+        <v>-1.266</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2957</v>
+        <v>-1.266</v>
       </c>
       <c r="N40" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3337</v>
+        <v>-1.3789</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.786</v>
+        <v>-0.8127</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2401</v>
+        <v>-1.2519</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3337</v>
+        <v>-1.3789</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3337</v>
+        <v>-1.3789</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3337</v>
+        <v>-1.3789</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3337</v>
+        <v>-1.3789</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3337</v>
+        <v>-1.3789</v>
       </c>
       <c r="N41" t="n">
         <v>235</v>
@@ -2429,10 +2429,10 @@
         <v>2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J2" t="n">
-        <v>35.4939</v>
+        <v>35.0607</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.69</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3049</v>
+        <v>1.3931</v>
       </c>
       <c r="J3" t="n">
-        <v>24.7931</v>
+        <v>26.4689</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.922</v>
+        <v>0.8796</v>
       </c>
       <c r="J4" t="n">
-        <v>17.518</v>
+        <v>16.7124</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.29</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6849</v>
       </c>
       <c r="J5" t="n">
-        <v>13.3209</v>
+        <v>13.0131</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0308</v>
+        <v>0.0128</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5852000000000001</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5095</v>
       </c>
       <c r="J7" t="n">
-        <v>11.0409</v>
+        <v>9.6805</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4032</v>
+        <v>-0.4231</v>
       </c>
       <c r="J8" t="n">
-        <v>-7.6608</v>
+        <v>-8.0389</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.4</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5523</v>
+        <v>-0.5622</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.4937</v>
+        <v>-10.6818</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.36</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.591</v>
+        <v>-0.5979</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.229</v>
+        <v>-11.3601</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.36</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.591</v>
+        <v>-0.5979</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.229</v>
+        <v>-11.3601</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.59</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2183</v>
+        <v>1.2601</v>
       </c>
       <c r="J12" t="n">
-        <v>28.0209</v>
+        <v>28.9823</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1457</v>
+        <v>1.1546</v>
       </c>
       <c r="J13" t="n">
-        <v>26.3511</v>
+        <v>26.5558</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9201</v>
       </c>
       <c r="J14" t="n">
-        <v>22.3169</v>
+        <v>21.1623</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4007</v>
+        <v>0.4084</v>
       </c>
       <c r="J15" t="n">
-        <v>9.216100000000001</v>
+        <v>9.3932</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.15</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4007</v>
+        <v>0.4084</v>
       </c>
       <c r="J16" t="n">
-        <v>9.216100000000001</v>
+        <v>9.3932</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.22</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5955</v>
+        <v>0.5564</v>
       </c>
       <c r="J17" t="n">
-        <v>13.6965</v>
+        <v>12.7972</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1463</v>
+        <v>0.132</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3649</v>
+        <v>3.036</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.62</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3803</v>
+        <v>-0.3957</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.7469</v>
+        <v>-9.101100000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4922</v>
+        <v>-0.5014</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.3206</v>
+        <v>-11.5322</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.45</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5384</v>
+        <v>-0.5447</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.3832</v>
+        <v>-12.5281</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6387</v>
+        <v>0.6133</v>
       </c>
       <c r="J22" t="n">
-        <v>17.8836</v>
+        <v>17.1724</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0321</v>
+        <v>-0.0398</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8988</v>
+        <v>-1.1144</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.92</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1063</v>
+        <v>-0.1195</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9764</v>
+        <v>-3.346</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1922</v>
+        <v>-0.2071</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.3816</v>
+        <v>-5.7988</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3302</v>
+        <v>-0.3429</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.2456</v>
+        <v>-9.6012</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.43</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0425</v>
+        <v>0.9932</v>
       </c>
       <c r="J27" t="n">
-        <v>29.19</v>
+        <v>27.8096</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8968</v>
+        <v>0.8454</v>
       </c>
       <c r="J28" t="n">
-        <v>25.1104</v>
+        <v>23.6712</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5056</v>
+        <v>0.4973</v>
       </c>
       <c r="J29" t="n">
-        <v>14.1568</v>
+        <v>13.9244</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3221</v>
+        <v>0.3302</v>
       </c>
       <c r="J30" t="n">
-        <v>9.018800000000001</v>
+        <v>9.2456</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.11</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3221</v>
+        <v>0.3302</v>
       </c>
       <c r="J31" t="n">
-        <v>9.018800000000001</v>
+        <v>9.2456</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1827</v>
+        <v>-0.2067</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.8367</v>
+        <v>-4.3407</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.7</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2941</v>
+        <v>-0.315</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.1761</v>
+        <v>-6.615</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.65</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3387</v>
+        <v>-0.3583</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.1127</v>
+        <v>-7.5243</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3661</v>
+        <v>-0.3846</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.6881</v>
+        <v>-8.076599999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.58</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4032</v>
+        <v>-0.4199</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.4672</v>
+        <v>-8.8179</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.58</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1896</v>
+        <v>1.1659</v>
       </c>
       <c r="J37" t="n">
-        <v>24.9816</v>
+        <v>24.4839</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.55</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1545</v>
+        <v>1.128</v>
       </c>
       <c r="J38" t="n">
-        <v>24.2445</v>
+        <v>23.688</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.55</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1545</v>
+        <v>1.128</v>
       </c>
       <c r="J39" t="n">
-        <v>24.2445</v>
+        <v>23.688</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.44</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0223</v>
+        <v>0.978</v>
       </c>
       <c r="J40" t="n">
-        <v>21.4683</v>
+        <v>20.538</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.25</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6254</v>
+        <v>0.6146</v>
       </c>
       <c r="J41" t="n">
-        <v>13.1334</v>
+        <v>12.9066</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.78</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8551</v>
+        <v>0.8485</v>
       </c>
       <c r="J42" t="n">
-        <v>18.8122</v>
+        <v>18.667</v>
       </c>
     </row>
     <row r="43">
@@ -4109,10 +4109,10 @@
         <v>1.45</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5312</v>
+        <v>0.5456</v>
       </c>
       <c r="J44" t="n">
-        <v>11.6864</v>
+        <v>12.0032</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.4</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4786</v>
+        <v>0.4956</v>
       </c>
       <c r="J45" t="n">
-        <v>10.5292</v>
+        <v>10.9032</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.29</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3565</v>
+        <v>0.3787</v>
       </c>
       <c r="J46" t="n">
-        <v>7.843</v>
+        <v>8.3314</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.92</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.063</v>
+        <v>-0.0859</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.386</v>
+        <v>-1.8898</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.87</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1233</v>
+        <v>-0.1465</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.7126</v>
+        <v>-3.223</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.76</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2409</v>
+        <v>-0.2623</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.2998</v>
+        <v>-5.7706</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4173</v>
+        <v>-0.4324</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.1806</v>
+        <v>-9.5128</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.38</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5948</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.0856</v>
+        <v>-13.1626</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.32</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7591</v>
+        <v>0.7083</v>
       </c>
       <c r="J52" t="n">
-        <v>17.4593</v>
+        <v>16.2909</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.83</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1868</v>
+        <v>-0.2054</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.2964</v>
+        <v>-4.7242</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1967</v>
+        <v>-0.2153</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.5241</v>
+        <v>-4.9519</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4422</v>
+        <v>-0.4535</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.1706</v>
+        <v>-10.4305</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.48</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5161</v>
+        <v>-0.523</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.8703</v>
+        <v>-12.029</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.65</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2945</v>
+        <v>1.2739</v>
       </c>
       <c r="J57" t="n">
-        <v>29.7735</v>
+        <v>29.2997</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.47</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0754</v>
+        <v>1.0368</v>
       </c>
       <c r="J58" t="n">
-        <v>24.7342</v>
+        <v>23.8464</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.38</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9359</v>
+        <v>0.8855</v>
       </c>
       <c r="J59" t="n">
-        <v>21.5257</v>
+        <v>20.3665</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.2</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5321</v>
+        <v>0.526</v>
       </c>
       <c r="J60" t="n">
-        <v>12.2383</v>
+        <v>12.098</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.02</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0131</v>
+        <v>0.0437</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3013</v>
+        <v>1.0051</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.15</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3334</v>
+        <v>0.3378</v>
       </c>
       <c r="J62" t="n">
-        <v>10.002</v>
+        <v>10.134</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1751</v>
+        <v>0.1855</v>
       </c>
       <c r="J63" t="n">
-        <v>5.253</v>
+        <v>5.565</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.04</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1099</v>
+        <v>0.1203</v>
       </c>
       <c r="J64" t="n">
-        <v>3.297</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0862</v>
+        <v>0.0961</v>
       </c>
       <c r="J65" t="n">
-        <v>2.586</v>
+        <v>2.883</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1047</v>
+        <v>-0.1151</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.141</v>
+        <v>-3.453</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.71</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4291</v>
+        <v>1.4058</v>
       </c>
       <c r="J67" t="n">
-        <v>42.873</v>
+        <v>42.174</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5246</v>
+        <v>0.5102</v>
       </c>
       <c r="J68" t="n">
-        <v>15.738</v>
+        <v>15.306</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.09</v>
       </c>
       <c r="I69" t="n">
-        <v>0.29</v>
+        <v>0.2949</v>
       </c>
       <c r="J69" t="n">
-        <v>8.699999999999999</v>
+        <v>8.847</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4425</v>
+        <v>-0.4197</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.275</v>
+        <v>-12.591</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.79</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6835</v>
+        <v>-0.636</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.505</v>
+        <v>-19.08</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4091</v>
+        <v>1.4044</v>
       </c>
       <c r="J72" t="n">
-        <v>28.182</v>
+        <v>28.088</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.74</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3538</v>
+        <v>1.3455</v>
       </c>
       <c r="J73" t="n">
-        <v>27.076</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.71</v>
       </c>
       <c r="I74" t="n">
-        <v>1.3205</v>
+        <v>1.31</v>
       </c>
       <c r="J74" t="n">
-        <v>26.41</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.56</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1538</v>
+        <v>1.1301</v>
       </c>
       <c r="J75" t="n">
-        <v>23.076</v>
+        <v>22.602</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.31</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7353</v>
+        <v>0.7171</v>
       </c>
       <c r="J76" t="n">
-        <v>14.706</v>
+        <v>14.342</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.6</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.3436</v>
+        <v>-0.3706</v>
       </c>
       <c r="J77" t="n">
-        <v>-6.872</v>
+        <v>-7.412</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.51</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4341</v>
+        <v>-0.4548</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.682</v>
+        <v>-9.096</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.47</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4691</v>
+        <v>-0.4878</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.382</v>
+        <v>-9.756</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.43</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5061</v>
+        <v>-0.5221</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.122</v>
+        <v>-10.442</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5349</v>
+        <v>-0.5486</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.698</v>
+        <v>-10.972</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.23</v>
       </c>
       <c r="I82" t="n">
-        <v>0.379</v>
+        <v>0.3804</v>
       </c>
       <c r="J82" t="n">
-        <v>10.233</v>
+        <v>10.2708</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1075</v>
+        <v>0.1165</v>
       </c>
       <c r="J83" t="n">
-        <v>2.9025</v>
+        <v>3.1455</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.111</v>
+        <v>-0.1231</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.997</v>
+        <v>-3.3237</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.91</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1224</v>
+        <v>-0.1349</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.3048</v>
+        <v>-3.6423</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.86</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1768</v>
+        <v>-0.1904</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.7736</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.61</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7731</v>
+        <v>0.759</v>
       </c>
       <c r="J87" t="n">
-        <v>20.8737</v>
+        <v>20.493</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.19</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2821</v>
+        <v>0.2965</v>
       </c>
       <c r="J88" t="n">
-        <v>7.6167</v>
+        <v>8.0055</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.9548</v>
+        <v>-2.1492</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.9</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1441</v>
+        <v>-0.1546</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.8907</v>
+        <v>-4.1742</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2589</v>
+        <v>-0.2701</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.9903</v>
+        <v>-7.2927</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.22</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6248</v>
+        <v>0.5997</v>
       </c>
       <c r="J92" t="n">
-        <v>18.1192</v>
+        <v>17.3913</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.2</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5755</v>
+        <v>0.5557</v>
       </c>
       <c r="J93" t="n">
-        <v>16.6895</v>
+        <v>16.1153</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.14</v>
       </c>
       <c r="I94" t="n">
-        <v>0.424</v>
+        <v>0.4186</v>
       </c>
       <c r="J94" t="n">
-        <v>12.296</v>
+        <v>12.1394</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.14</v>
       </c>
       <c r="I95" t="n">
-        <v>0.424</v>
+        <v>0.4186</v>
       </c>
       <c r="J95" t="n">
-        <v>12.296</v>
+        <v>12.1394</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2947</v>
+        <v>-0.2836</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.5463</v>
+        <v>-8.224399999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.99</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.0157</v>
+        <v>-0.0215</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.4553</v>
+        <v>-0.6235000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.98</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0314</v>
+        <v>-0.0393</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.9106</v>
+        <v>-1.1397</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.93</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0944</v>
+        <v>-0.1072</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.7376</v>
+        <v>-3.1088</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1058</v>
+        <v>-0.1191</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.0682</v>
+        <v>-3.4539</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.89</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1388</v>
+        <v>-0.1533</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.0252</v>
+        <v>-4.4457</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2986</v>
+        <v>0.2907</v>
       </c>
       <c r="J102" t="n">
-        <v>7.1664</v>
+        <v>6.9768</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0994</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.0184</v>
+        <v>-2.3856</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.88</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1407</v>
+        <v>-0.1575</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.3768</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2205</v>
+        <v>-0.238</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.292</v>
+        <v>-5.712</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.53</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.476</v>
+        <v>-0.4845</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.424</v>
+        <v>-11.628</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.52</v>
       </c>
       <c r="I107" t="n">
-        <v>1.143</v>
+        <v>1.1105</v>
       </c>
       <c r="J107" t="n">
-        <v>27.432</v>
+        <v>26.652</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.143</v>
+        <v>1.1105</v>
       </c>
       <c r="J108" t="n">
-        <v>27.432</v>
+        <v>26.652</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.18</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4897</v>
+        <v>0.4863</v>
       </c>
       <c r="J109" t="n">
-        <v>11.7528</v>
+        <v>11.6712</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4644</v>
+        <v>0.4635</v>
       </c>
       <c r="J110" t="n">
-        <v>11.1456</v>
+        <v>11.124</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.16</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4387</v>
+        <v>0.4403</v>
       </c>
       <c r="J111" t="n">
-        <v>10.5288</v>
+        <v>10.5672</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.85</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1124</v>
+        <v>-0.1426</v>
       </c>
       <c r="J112" t="n">
-        <v>-2.0232</v>
+        <v>-2.5668</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.65</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3278</v>
+        <v>-0.35</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.9004</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3997</v>
+        <v>-0.4188</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.1946</v>
+        <v>-7.5384</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.51</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4552</v>
+        <v>-0.471</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.1936</v>
+        <v>-8.478</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.41</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.55</v>
+        <v>-0.5592</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.9</v>
+        <v>-10.0656</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.93</v>
       </c>
       <c r="I117" t="n">
-        <v>1.5677</v>
+        <v>1.5713</v>
       </c>
       <c r="J117" t="n">
-        <v>28.2186</v>
+        <v>28.2834</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.66</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2678</v>
+        <v>1.2529</v>
       </c>
       <c r="J118" t="n">
-        <v>22.8204</v>
+        <v>22.5522</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.57</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1677</v>
+        <v>1.1446</v>
       </c>
       <c r="J119" t="n">
-        <v>21.0186</v>
+        <v>20.6028</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.43</v>
       </c>
       <c r="I120" t="n">
-        <v>0.9917</v>
+        <v>0.9483</v>
       </c>
       <c r="J120" t="n">
-        <v>17.8506</v>
+        <v>17.0694</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.37</v>
       </c>
       <c r="I121" t="n">
-        <v>0.8741</v>
+        <v>0.8379</v>
       </c>
       <c r="J121" t="n">
-        <v>15.7338</v>
+        <v>15.0822</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.99</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0184</v>
+        <v>-0.0016</v>
       </c>
       <c r="J122" t="n">
-        <v>0.4784</v>
+        <v>-0.0416</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.92</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.1046</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.2594</v>
+        <v>-2.7196</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1105</v>
+        <v>-0.1287</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.873</v>
+        <v>-3.3462</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.64</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3666</v>
+        <v>-0.3817</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.531599999999999</v>
+        <v>-9.924200000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.53</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4692</v>
+        <v>-0.4791</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.1992</v>
+        <v>-12.4566</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.66</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3338</v>
+        <v>1.3108</v>
       </c>
       <c r="J127" t="n">
-        <v>34.6788</v>
+        <v>34.0808</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.26</v>
       </c>
       <c r="I128" t="n">
-        <v>0.694</v>
+        <v>0.6665</v>
       </c>
       <c r="J128" t="n">
-        <v>18.044</v>
+        <v>17.329</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.694</v>
+        <v>0.6665</v>
       </c>
       <c r="J129" t="n">
-        <v>18.044</v>
+        <v>17.329</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6028</v>
+        <v>0.5847</v>
       </c>
       <c r="J130" t="n">
-        <v>15.6728</v>
+        <v>15.2022</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.784</v>
+        <v>-0.7205</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.384</v>
+        <v>-18.733</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5557</v>
+        <v>0.5639</v>
       </c>
       <c r="J132" t="n">
-        <v>13.3368</v>
+        <v>13.5336</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.33</v>
       </c>
       <c r="I133" t="n">
-        <v>0.424</v>
+        <v>0.4388</v>
       </c>
       <c r="J133" t="n">
-        <v>10.176</v>
+        <v>10.5312</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.31</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4017</v>
+        <v>0.4174</v>
       </c>
       <c r="J134" t="n">
-        <v>9.6408</v>
+        <v>10.0176</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.2</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2751</v>
+        <v>0.2942</v>
       </c>
       <c r="J135" t="n">
-        <v>6.6024</v>
+        <v>7.0608</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.08</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1142</v>
+        <v>0.1341</v>
       </c>
       <c r="J136" t="n">
-        <v>2.7408</v>
+        <v>3.2184</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.14</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2965</v>
+        <v>0.2924</v>
       </c>
       <c r="J137" t="n">
-        <v>7.116</v>
+        <v>7.0176</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1809</v>
+        <v>0.1802</v>
       </c>
       <c r="J138" t="n">
-        <v>4.3416</v>
+        <v>4.3248</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1286</v>
+        <v>-0.1455</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.0864</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.55</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4564</v>
+        <v>-0.4661</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.9536</v>
+        <v>-11.1864</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4656</v>
+        <v>-0.4748</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.1744</v>
+        <v>-11.3952</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.578</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>13.294</v>
+        <v>12.6477</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1066</v>
+        <v>0.1028</v>
       </c>
       <c r="J143" t="n">
-        <v>2.4518</v>
+        <v>2.3644</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0963</v>
+        <v>-0.1119</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.2149</v>
+        <v>-2.5737</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.57</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4394</v>
+        <v>-0.4498</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.1062</v>
+        <v>-10.3454</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5037</v>
+        <v>-0.5105</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.5851</v>
+        <v>-11.7415</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>1.057</v>
+        <v>1.0103</v>
       </c>
       <c r="J147" t="n">
-        <v>24.311</v>
+        <v>23.2369</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0136</v>
+        <v>0.9597</v>
       </c>
       <c r="J148" t="n">
-        <v>23.3128</v>
+        <v>22.0731</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6028</v>
+        <v>0.5847</v>
       </c>
       <c r="J149" t="n">
-        <v>13.8644</v>
+        <v>13.4481</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.295</v>
+        <v>0.305</v>
       </c>
       <c r="J150" t="n">
-        <v>6.785</v>
+        <v>7.015</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.99</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1115</v>
+        <v>-0.099</v>
       </c>
       <c r="J151" t="n">
-        <v>-2.5645</v>
+        <v>-2.277</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8105</v>
+        <v>0.7605</v>
       </c>
       <c r="J152" t="n">
-        <v>29.178</v>
+        <v>27.378</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.26</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7378</v>
+        <v>0.6968</v>
       </c>
       <c r="J153" t="n">
-        <v>26.5608</v>
+        <v>25.0848</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5889</v>
+        <v>0.5649</v>
       </c>
       <c r="J154" t="n">
-        <v>21.2004</v>
+        <v>20.3364</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2118</v>
+        <v>0.2187</v>
       </c>
       <c r="J155" t="n">
-        <v>7.6248</v>
+        <v>7.8732</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.136</v>
+        <v>-1.032</v>
       </c>
       <c r="J156" t="n">
-        <v>-40.896</v>
+        <v>-37.152</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.639</v>
+        <v>0.6194</v>
       </c>
       <c r="J157" t="n">
-        <v>23.004</v>
+        <v>22.2984</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6048</v>
+        <v>0.5883</v>
       </c>
       <c r="J158" t="n">
-        <v>21.7728</v>
+        <v>21.1788</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.1</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2386</v>
+        <v>0.2469</v>
       </c>
       <c r="J159" t="n">
-        <v>8.589600000000001</v>
+        <v>8.888400000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2529</v>
+        <v>-0.2653</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.1044</v>
+        <v>-9.550800000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3775</v>
+        <v>-0.3869</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.59</v>
+        <v>-13.9284</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.17</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5022</v>
       </c>
       <c r="J162" t="n">
-        <v>15.621</v>
+        <v>15.066</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.12</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3872</v>
+        <v>0.3812</v>
       </c>
       <c r="J163" t="n">
-        <v>11.616</v>
+        <v>11.436</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0832</v>
+        <v>0.0925</v>
       </c>
       <c r="J164" t="n">
-        <v>2.496</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0117</v>
+        <v>-0.008</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.351</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.97</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1442</v>
+        <v>-0.1452</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.326</v>
+        <v>-4.356</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8446</v>
+        <v>0.8035</v>
       </c>
       <c r="J167" t="n">
-        <v>25.338</v>
+        <v>24.105</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4501</v>
+        <v>0.4456</v>
       </c>
       <c r="J168" t="n">
-        <v>13.503</v>
+        <v>13.368</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.09</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2208</v>
+        <v>0.2291</v>
       </c>
       <c r="J169" t="n">
-        <v>6.624</v>
+        <v>6.873</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.75</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2908</v>
+        <v>-0.3029</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.724</v>
+        <v>-9.087</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.62</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4132</v>
+        <v>-0.4215</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.396</v>
+        <v>-12.645</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.58</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2278</v>
+        <v>1.1994</v>
       </c>
       <c r="J172" t="n">
-        <v>31.9228</v>
+        <v>31.1844</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.47</v>
       </c>
       <c r="I173" t="n">
-        <v>1.09</v>
+        <v>1.0505</v>
       </c>
       <c r="J173" t="n">
-        <v>28.34</v>
+        <v>27.313</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5254</v>
+        <v>0.5162</v>
       </c>
       <c r="J174" t="n">
-        <v>13.6604</v>
+        <v>13.4212</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.03</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0698</v>
+        <v>0.0939</v>
       </c>
       <c r="J175" t="n">
-        <v>1.8148</v>
+        <v>2.4414</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.03</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0698</v>
+        <v>0.0939</v>
       </c>
       <c r="J176" t="n">
-        <v>1.8148</v>
+        <v>2.4414</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.19</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5063</v>
+        <v>0.48</v>
       </c>
       <c r="J177" t="n">
-        <v>13.1638</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.319</v>
+        <v>0.3057</v>
       </c>
       <c r="J178" t="n">
-        <v>8.294</v>
+        <v>7.9482</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.63</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3775</v>
+        <v>-0.3918</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.815</v>
+        <v>-10.1868</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.62</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3869</v>
+        <v>-0.4008</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.0594</v>
+        <v>-10.4208</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.49</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5074</v>
+        <v>-0.5148</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.1924</v>
+        <v>-13.3848</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.31</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4658</v>
+        <v>0.4654</v>
       </c>
       <c r="J182" t="n">
-        <v>13.974</v>
+        <v>13.962</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3872</v>
+        <v>0.3917</v>
       </c>
       <c r="J183" t="n">
-        <v>11.616</v>
+        <v>11.751</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1153</v>
+        <v>0.1271</v>
       </c>
       <c r="J184" t="n">
-        <v>3.459</v>
+        <v>3.813</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.081</v>
+        <v>0.0919</v>
       </c>
       <c r="J185" t="n">
-        <v>2.43</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.71</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3347</v>
+        <v>-0.3447</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.041</v>
+        <v>-10.341</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.18</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2822</v>
+        <v>0.2938</v>
       </c>
       <c r="J187" t="n">
-        <v>8.465999999999999</v>
+        <v>8.814</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1431</v>
+        <v>0.1557</v>
       </c>
       <c r="J188" t="n">
-        <v>4.293</v>
+        <v>4.671</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.01</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0256</v>
+        <v>0.0313</v>
       </c>
       <c r="J189" t="n">
-        <v>0.768</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.022</v>
+        <v>-0.0263</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.66</v>
+        <v>-0.789</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2107</v>
+        <v>-0.2238</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.321</v>
+        <v>-6.714</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.441</v>
+        <v>1.4324</v>
       </c>
       <c r="J192" t="n">
-        <v>28.82</v>
+        <v>28.648</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1719</v>
+        <v>1.1456</v>
       </c>
       <c r="J193" t="n">
-        <v>23.438</v>
+        <v>22.912</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.47</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0644</v>
+        <v>1.0265</v>
       </c>
       <c r="J194" t="n">
-        <v>21.288</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.28</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7044</v>
+        <v>0.6829</v>
       </c>
       <c r="J195" t="n">
-        <v>14.088</v>
+        <v>13.658</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1326</v>
       </c>
       <c r="J196" t="n">
-        <v>1.992</v>
+        <v>2.652</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3705</v>
+        <v>0.3345</v>
       </c>
       <c r="J197" t="n">
-        <v>7.41</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.73</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2633</v>
+        <v>-0.2855</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.266</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.67</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3201</v>
+        <v>-0.3405</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.402</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.58</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4015</v>
+        <v>-0.4185</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.029999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.25</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7117</v>
+        <v>-0.7064</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.234</v>
+        <v>-14.128</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7289</v>
+        <v>0.6816</v>
       </c>
       <c r="J202" t="n">
-        <v>21.867</v>
+        <v>20.448</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.11</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3812</v>
+        <v>0.3708</v>
       </c>
       <c r="J203" t="n">
-        <v>11.436</v>
+        <v>11.124</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.99</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0519</v>
+        <v>-0.0577</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.557</v>
+        <v>-1.731</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.82</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5657</v>
+        <v>-0.5387</v>
       </c>
       <c r="J205" t="n">
-        <v>-16.971</v>
+        <v>-16.161</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.79</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.644</v>
+        <v>-0.6083</v>
       </c>
       <c r="J206" t="n">
-        <v>-19.32</v>
+        <v>-18.249</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5641</v>
+        <v>0.5554</v>
       </c>
       <c r="J207" t="n">
-        <v>16.923</v>
+        <v>16.662</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.26</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5133</v>
+        <v>0.5087</v>
       </c>
       <c r="J208" t="n">
-        <v>15.399</v>
+        <v>15.261</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.06</v>
       </c>
       <c r="I209" t="n">
-        <v>0.145</v>
+        <v>0.1582</v>
       </c>
       <c r="J209" t="n">
-        <v>4.35</v>
+        <v>4.746</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.03</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0752</v>
+        <v>0.0882</v>
       </c>
       <c r="J210" t="n">
-        <v>2.256</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.92</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1237</v>
+        <v>-0.133</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.711</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0718</v>
+        <v>1.0276</v>
       </c>
       <c r="J212" t="n">
-        <v>31.0822</v>
+        <v>29.8004</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.25</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6725</v>
+        <v>0.647</v>
       </c>
       <c r="J213" t="n">
-        <v>19.5025</v>
+        <v>18.763</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6059</v>
       </c>
       <c r="J214" t="n">
-        <v>18.1685</v>
+        <v>17.5711</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.18</v>
       </c>
       <c r="I215" t="n">
-        <v>0.508</v>
+        <v>0.4989</v>
       </c>
       <c r="J215" t="n">
-        <v>14.732</v>
+        <v>14.4681</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.01</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0003</v>
+        <v>0.0221</v>
       </c>
       <c r="J216" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.6409</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.08</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2321</v>
+        <v>0.2322</v>
       </c>
       <c r="J217" t="n">
-        <v>6.7309</v>
+        <v>6.7338</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.05</v>
       </c>
       <c r="I218" t="n">
-        <v>0.164</v>
+        <v>0.1658</v>
       </c>
       <c r="J218" t="n">
-        <v>4.756</v>
+        <v>4.8082</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0413</v>
+        <v>-0.0516</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.1977</v>
+        <v>-1.4964</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.88</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1458</v>
+        <v>-0.1613</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.2282</v>
+        <v>-4.6777</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.55</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4647</v>
+        <v>-0.4726</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.4763</v>
+        <v>-13.7054</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.88</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1033</v>
+        <v>-0.1284</v>
       </c>
       <c r="J222" t="n">
-        <v>-2.3759</v>
+        <v>-2.9532</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.75</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2454</v>
+        <v>-0.2678</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.6442</v>
+        <v>-6.1594</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.62</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3661</v>
+        <v>-0.3846</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.420299999999999</v>
+        <v>-8.845800000000001</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4125</v>
+        <v>-0.4287</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.487500000000001</v>
+        <v>-9.860099999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4406</v>
+        <v>-0.4552</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.1338</v>
+        <v>-10.4696</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.71</v>
       </c>
       <c r="I227" t="n">
-        <v>1.357</v>
+        <v>1.3418</v>
       </c>
       <c r="J227" t="n">
-        <v>31.211</v>
+        <v>30.8614</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.58</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2026</v>
+        <v>1.1772</v>
       </c>
       <c r="J228" t="n">
-        <v>27.6598</v>
+        <v>27.0756</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.57</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1906</v>
+        <v>1.1643</v>
       </c>
       <c r="J229" t="n">
-        <v>27.3838</v>
+        <v>26.7789</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.22</v>
       </c>
       <c r="I230" t="n">
-        <v>0.572</v>
+        <v>0.5635</v>
       </c>
       <c r="J230" t="n">
-        <v>13.156</v>
+        <v>12.9605</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.584</v>
+        <v>-0.536</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.432</v>
+        <v>-12.328</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.08</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2098</v>
+        <v>0.2159</v>
       </c>
       <c r="J232" t="n">
-        <v>6.294</v>
+        <v>6.477</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0025</v>
+        <v>0.0018</v>
       </c>
       <c r="J233" t="n">
-        <v>0.075</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0194</v>
+        <v>-0.0244</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.582</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0346</v>
+        <v>-0.0417</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.038</v>
+        <v>-1.251</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1856</v>
+        <v>-0.1997</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.568</v>
+        <v>-5.991</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8601</v>
+        <v>0.8035</v>
       </c>
       <c r="J237" t="n">
-        <v>25.803</v>
+        <v>24.105</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.16</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4876</v>
+        <v>0.4738</v>
       </c>
       <c r="J238" t="n">
-        <v>14.628</v>
+        <v>14.214</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.15</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4614</v>
+        <v>0.4501</v>
       </c>
       <c r="J239" t="n">
-        <v>13.842</v>
+        <v>13.503</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.02</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0781</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>2.343</v>
+        <v>2.667</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7714</v>
+        <v>-0.716</v>
       </c>
       <c r="J241" t="n">
-        <v>-23.142</v>
+        <v>-21.48</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4163</v>
+        <v>0.4025</v>
       </c>
       <c r="J242" t="n">
-        <v>9.991199999999999</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.89</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1316</v>
+        <v>-0.1478</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.1584</v>
+        <v>-3.5472</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.88</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1423</v>
+        <v>-0.1587</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.4152</v>
+        <v>-3.8088</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.7</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3192</v>
+        <v>-0.3343</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.6608</v>
+        <v>-8.023199999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.68</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3382</v>
+        <v>-0.3527</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.1168</v>
+        <v>-8.4648</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>2.01</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7366</v>
+        <v>1.7354</v>
       </c>
       <c r="J247" t="n">
-        <v>41.6784</v>
+        <v>41.6496</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6414</v>
+        <v>0.621</v>
       </c>
       <c r="J248" t="n">
-        <v>15.3936</v>
+        <v>14.904</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6414</v>
+        <v>0.621</v>
       </c>
       <c r="J249" t="n">
-        <v>15.3936</v>
+        <v>14.904</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.07</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1957</v>
+        <v>0.2153</v>
       </c>
       <c r="J250" t="n">
-        <v>4.6968</v>
+        <v>5.1672</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5886</v>
+        <v>-0.5445</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.1264</v>
+        <v>-13.068</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.01</v>
       </c>
       <c r="I252" t="n">
-        <v>0.1103</v>
+        <v>0.0963</v>
       </c>
       <c r="J252" t="n">
-        <v>2.5369</v>
+        <v>2.2149</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.85</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1615</v>
+        <v>-0.1812</v>
       </c>
       <c r="J253" t="n">
-        <v>-3.7145</v>
+        <v>-4.1676</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.76</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2501</v>
+        <v>-0.2693</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.7523</v>
+        <v>-6.1939</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.64</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3631</v>
+        <v>-0.3789</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.3513</v>
+        <v>-8.714700000000001</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4006</v>
+        <v>-0.4147</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.213800000000001</v>
+        <v>-9.5381</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2101</v>
+        <v>1.1838</v>
       </c>
       <c r="J257" t="n">
-        <v>27.8323</v>
+        <v>27.2274</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.45</v>
       </c>
       <c r="I258" t="n">
-        <v>1.05</v>
+        <v>1.0067</v>
       </c>
       <c r="J258" t="n">
-        <v>24.15</v>
+        <v>23.1541</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.42</v>
       </c>
       <c r="I259" t="n">
-        <v>1.0071</v>
+        <v>0.9575</v>
       </c>
       <c r="J259" t="n">
-        <v>23.1633</v>
+        <v>22.0225</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.29</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7441</v>
+        <v>0.7147</v>
       </c>
       <c r="J260" t="n">
-        <v>17.1143</v>
+        <v>16.4381</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1788</v>
+        <v>-0.1588</v>
       </c>
       <c r="J261" t="n">
-        <v>-4.1124</v>
+        <v>-3.6524</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.52</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6279</v>
+        <v>0.632</v>
       </c>
       <c r="J262" t="n">
-        <v>13.8138</v>
+        <v>13.904</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.45</v>
       </c>
       <c r="I263" t="n">
-        <v>0.553</v>
+        <v>0.5618</v>
       </c>
       <c r="J263" t="n">
-        <v>12.166</v>
+        <v>12.3596</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.24</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3214</v>
+        <v>0.3398</v>
       </c>
       <c r="J264" t="n">
-        <v>7.0708</v>
+        <v>7.4756</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.23</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3096</v>
+        <v>0.3283</v>
       </c>
       <c r="J265" t="n">
-        <v>6.8112</v>
+        <v>7.2226</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.02</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0126</v>
+        <v>0.0286</v>
       </c>
       <c r="J266" t="n">
-        <v>0.2772</v>
+        <v>0.6292</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.97</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0264</v>
+        <v>-0.04</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.5808</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0911</v>
+        <v>-0.1079</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.0042</v>
+        <v>-2.3738</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.9</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1144</v>
+        <v>-0.1317</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.5168</v>
+        <v>-2.8974</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.71</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3035</v>
+        <v>-0.3203</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.677</v>
+        <v>-7.0466</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4166</v>
+        <v>-0.4288</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.1652</v>
+        <v>-9.4336</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5085</v>
+        <v>0.4987</v>
       </c>
       <c r="J272" t="n">
-        <v>15.255</v>
+        <v>14.961</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.12</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2845</v>
+        <v>0.2894</v>
       </c>
       <c r="J273" t="n">
-        <v>8.535</v>
+        <v>8.682</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.224</v>
+        <v>0.2313</v>
       </c>
       <c r="J274" t="n">
-        <v>6.72</v>
+        <v>6.939</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.88</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.157</v>
+        <v>-0.17</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.71</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3276</v>
+        <v>-0.3392</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.827999999999999</v>
+        <v>-10.176</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.23</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>19.611</v>
+        <v>18.735</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.17</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5039</v>
+        <v>0.4905</v>
       </c>
       <c r="J278" t="n">
-        <v>15.117</v>
+        <v>14.715</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.11</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3483</v>
+        <v>0.3482</v>
       </c>
       <c r="J279" t="n">
-        <v>10.449</v>
+        <v>10.446</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.09</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2937</v>
+        <v>0.2973</v>
       </c>
       <c r="J280" t="n">
-        <v>8.811</v>
+        <v>8.919</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.96</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.1941</v>
+        <v>-0.1893</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.823</v>
+        <v>-5.679</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.05</v>
       </c>
       <c r="I282" t="n">
-        <v>0.156</v>
+        <v>0.16</v>
       </c>
       <c r="J282" t="n">
-        <v>4.212</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0445</v>
+        <v>-0.0541</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.2015</v>
+        <v>-1.4607</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0445</v>
+        <v>-0.0541</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.2015</v>
+        <v>-1.4607</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0824</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.2248</v>
+        <v>-2.5569</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2995</v>
+        <v>-0.3135</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.086499999999999</v>
+        <v>-8.464499999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.49</v>
       </c>
       <c r="I287" t="n">
-        <v>1.141</v>
+        <v>1.1014</v>
       </c>
       <c r="J287" t="n">
-        <v>30.807</v>
+        <v>29.7378</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.29</v>
       </c>
       <c r="I288" t="n">
-        <v>0.7847</v>
+        <v>0.7425</v>
       </c>
       <c r="J288" t="n">
-        <v>21.1869</v>
+        <v>20.0475</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3135</v>
+        <v>0.3178</v>
       </c>
       <c r="J289" t="n">
-        <v>8.464499999999999</v>
+        <v>8.5806</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2381</v>
+        <v>-0.2286</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.4287</v>
+        <v>-6.1722</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.93</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3016</v>
+        <v>-0.2885</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.1432</v>
+        <v>-7.7895</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.28</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5764</v>
+        <v>0.5613</v>
       </c>
       <c r="J292" t="n">
-        <v>17.292</v>
+        <v>16.839</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.13</v>
       </c>
       <c r="I293" t="n">
-        <v>0.302</v>
+        <v>0.3066</v>
       </c>
       <c r="J293" t="n">
-        <v>9.06</v>
+        <v>9.198</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.03</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0893</v>
+        <v>0.0982</v>
       </c>
       <c r="J294" t="n">
-        <v>2.679</v>
+        <v>2.946</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.89</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1471</v>
+        <v>-0.1596</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.413</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.75</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2901</v>
+        <v>-0.3024</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.702999999999999</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.18</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5603</v>
+        <v>0.5349</v>
       </c>
       <c r="J297" t="n">
-        <v>16.809</v>
+        <v>16.047</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.11</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3705</v>
+        <v>0.3634</v>
       </c>
       <c r="J298" t="n">
-        <v>11.115</v>
+        <v>10.902</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0505</v>
+        <v>0.0568</v>
       </c>
       <c r="J299" t="n">
-        <v>1.515</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0034</v>
+        <v>-0.0023</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.102</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6271</v>
+        <v>-0.5916</v>
       </c>
       <c r="J301" t="n">
-        <v>-18.813</v>
+        <v>-17.748</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.23</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5244</v>
+        <v>0.507</v>
       </c>
       <c r="J302" t="n">
-        <v>13.11</v>
+        <v>12.675</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.97</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0431</v>
+        <v>-0.053</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.0775</v>
+        <v>-1.325</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1258</v>
+        <v>-0.1405</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.145</v>
+        <v>-3.5125</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1682</v>
+        <v>-0.1838</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.205</v>
+        <v>-4.595</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.64</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3833</v>
+        <v>-0.3947</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.5825</v>
+        <v>-9.8675</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.88</v>
       </c>
       <c r="I307" t="n">
-        <v>1.6038</v>
+        <v>1.5941</v>
       </c>
       <c r="J307" t="n">
-        <v>40.095</v>
+        <v>39.8525</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.25</v>
       </c>
       <c r="I308" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6473</v>
       </c>
       <c r="J308" t="n">
-        <v>16.8225</v>
+        <v>16.1825</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.21</v>
       </c>
       <c r="I309" t="n">
-        <v>0.5809</v>
+        <v>0.5646</v>
       </c>
       <c r="J309" t="n">
-        <v>14.5225</v>
+        <v>14.115</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.98</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1502</v>
+        <v>-0.1387</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.755</v>
+        <v>-3.4675</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.79</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7059</v>
+        <v>-0.6518</v>
       </c>
       <c r="J311" t="n">
-        <v>-17.6475</v>
+        <v>-16.295</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6615</v>
+        <v>0.6242</v>
       </c>
       <c r="J312" t="n">
-        <v>16.5375</v>
+        <v>15.605</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1121</v>
+        <v>0.1068</v>
       </c>
       <c r="J313" t="n">
-        <v>2.8025</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.74</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2773</v>
+        <v>-0.2942</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.9325</v>
+        <v>-7.355</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.7</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3156</v>
+        <v>-0.3315</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.89</v>
+        <v>-8.2875</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.44</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5567</v>
+        <v>-0.5605</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.9175</v>
+        <v>-14.0125</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.59</v>
       </c>
       <c r="I317" t="n">
-        <v>1.2451</v>
+        <v>1.2169</v>
       </c>
       <c r="J317" t="n">
-        <v>31.1275</v>
+        <v>30.4225</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.38</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9585</v>
+        <v>0.9026</v>
       </c>
       <c r="J318" t="n">
-        <v>23.9625</v>
+        <v>22.565</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.18</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5048</v>
+        <v>0.4967</v>
       </c>
       <c r="J319" t="n">
-        <v>12.62</v>
+        <v>12.4175</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.08</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2352</v>
+        <v>0.25</v>
       </c>
       <c r="J320" t="n">
-        <v>5.88</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.97</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1919</v>
+        <v>-0.1785</v>
       </c>
       <c r="J321" t="n">
-        <v>-4.7975</v>
+        <v>-4.4625</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.92</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.1021</v>
       </c>
       <c r="J322" t="n">
-        <v>-1.9228</v>
+        <v>-2.3483</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.85</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1629</v>
+        <v>-0.1822</v>
       </c>
       <c r="J323" t="n">
-        <v>-3.7467</v>
+        <v>-4.1906</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.73</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2793</v>
+        <v>-0.2977</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.4239</v>
+        <v>-6.8471</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2793</v>
+        <v>-0.2977</v>
       </c>
       <c r="J325" t="n">
-        <v>-6.4239</v>
+        <v>-6.8471</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.336</v>
+        <v>-0.3527</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.728</v>
+        <v>-8.1121</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.76</v>
       </c>
       <c r="I327" t="n">
-        <v>1.4201</v>
+        <v>1.4079</v>
       </c>
       <c r="J327" t="n">
-        <v>32.6623</v>
+        <v>32.3817</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.52</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1333</v>
+        <v>1.102</v>
       </c>
       <c r="J328" t="n">
-        <v>26.0659</v>
+        <v>25.346</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.46</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0597</v>
+        <v>1.019</v>
       </c>
       <c r="J329" t="n">
-        <v>24.3731</v>
+        <v>23.437</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.33</v>
       </c>
       <c r="I330" t="n">
-        <v>0.8288</v>
+        <v>0.7903</v>
       </c>
       <c r="J330" t="n">
-        <v>19.0624</v>
+        <v>18.1769</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.76</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8113</v>
+        <v>-0.7398</v>
       </c>
       <c r="J331" t="n">
-        <v>-18.6599</v>
+        <v>-17.0154</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.79</v>
       </c>
       <c r="I332" t="n">
-        <v>1.4291</v>
+        <v>1.4219</v>
       </c>
       <c r="J332" t="n">
-        <v>30.0111</v>
+        <v>29.8599</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.69</v>
       </c>
       <c r="I333" t="n">
-        <v>1.3147</v>
+        <v>1.3004</v>
       </c>
       <c r="J333" t="n">
-        <v>27.6087</v>
+        <v>27.3084</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.5</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0945</v>
+        <v>1.0628</v>
       </c>
       <c r="J334" t="n">
-        <v>22.9845</v>
+        <v>22.3188</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.5</v>
       </c>
       <c r="I335" t="n">
-        <v>1.0945</v>
+        <v>1.0628</v>
       </c>
       <c r="J335" t="n">
-        <v>22.9845</v>
+        <v>22.3188</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.98</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2092</v>
+        <v>-0.1801</v>
       </c>
       <c r="J336" t="n">
-        <v>-4.3932</v>
+        <v>-3.7821</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.82</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1378</v>
+        <v>-0.1693</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.8938</v>
+        <v>-3.5553</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.2815</v>
+        <v>-0.307</v>
       </c>
       <c r="J338" t="n">
-        <v>-5.9115</v>
+        <v>-6.447</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.59</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3791</v>
+        <v>-0.3998</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.9611</v>
+        <v>-8.395799999999999</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.43</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5262</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J340" t="n">
-        <v>-11.0502</v>
+        <v>-11.2938</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.34</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6131</v>
+        <v>-0.6177</v>
       </c>
       <c r="J341" t="n">
-        <v>-12.8751</v>
+        <v>-12.9717</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2257</v>
+        <v>1.1952</v>
       </c>
       <c r="J342" t="n">
-        <v>28.1911</v>
+        <v>27.4896</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.35</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9019</v>
+        <v>0.849</v>
       </c>
       <c r="J343" t="n">
-        <v>20.7437</v>
+        <v>19.527</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.29</v>
       </c>
       <c r="I344" t="n">
-        <v>0.7659</v>
+        <v>0.7295</v>
       </c>
       <c r="J344" t="n">
-        <v>17.6157</v>
+        <v>16.7785</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.99</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1081</v>
+        <v>-0.0965</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.4863</v>
+        <v>-2.2195</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.89</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4367</v>
+        <v>-0.4096</v>
       </c>
       <c r="J346" t="n">
-        <v>-10.0441</v>
+        <v>-9.4208</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.98</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.0159</v>
+        <v>-0.0273</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.3657</v>
+        <v>-0.6279</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.98</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.0159</v>
+        <v>-0.0273</v>
       </c>
       <c r="J348" t="n">
-        <v>-0.3657</v>
+        <v>-0.6279</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.92</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0948</v>
+        <v>-0.1107</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.1804</v>
+        <v>-2.5461</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3257</v>
+        <v>-0.3411</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.4911</v>
+        <v>-7.8453</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.63</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3823</v>
+        <v>-0.3956</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.792899999999999</v>
+        <v>-9.098800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1978/event_1978_evp_summary.xlsx
+++ b/database/event/1978/event_1978_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7825</v>
+        <v>6.7612</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9974</v>
+        <v>3.9848</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4633</v>
+        <v>2.4743</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7825</v>
+        <v>6.7612</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1293</v>
+        <v>4.0434</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6532</v>
+        <v>2.7178</v>
       </c>
       <c r="H2" t="n">
-        <v>6.3128</v>
+        <v>6.3162</v>
       </c>
       <c r="I2" t="n">
-        <v>6.3128</v>
+        <v>6.3162</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6532</v>
+        <v>2.7178</v>
       </c>
       <c r="K2" t="n">
         <v>313</v>
@@ -529,7 +529,7 @@
         <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>8.966000000000001</v>
+        <v>9.034000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>355</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4911</v>
+        <v>5.3819</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2363</v>
+        <v>3.1719</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8755</v>
+        <v>1.8459</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4911</v>
+        <v>5.3819</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6516</v>
+        <v>3.549</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8395</v>
+        <v>1.8329</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2673</v>
+        <v>5.1832</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2673</v>
+        <v>5.1832</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8395</v>
+        <v>1.8329</v>
       </c>
       <c r="K3" t="n">
         <v>313</v>
@@ -575,7 +575,7 @@
         <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>7.1068</v>
+        <v>7.0161</v>
       </c>
       <c r="N3" t="n">
         <v>355</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3231</v>
+        <v>5.1332</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1373</v>
+        <v>3.0254</v>
       </c>
       <c r="D4" t="n">
-        <v>1.799</v>
+        <v>1.7326</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3231</v>
+        <v>5.1332</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6816</v>
+        <v>4.5059</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6415</v>
+        <v>0.6272</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5217</v>
+        <v>7.3761</v>
       </c>
       <c r="I4" t="n">
-        <v>7.5217</v>
+        <v>7.3761</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6415</v>
+        <v>0.6272</v>
       </c>
       <c r="K4" t="n">
         <v>290</v>
@@ -621,7 +621,7 @@
         <v>42</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1632</v>
+        <v>8.003299999999999</v>
       </c>
       <c r="N4" t="n">
         <v>332</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0231</v>
+        <v>5.1175</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9605</v>
+        <v>3.0161</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6624</v>
+        <v>1.7255</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0231</v>
+        <v>5.1175</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7694</v>
+        <v>2.7585</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2537</v>
+        <v>2.359</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3364</v>
+        <v>3.3716</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3364</v>
+        <v>3.3716</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2537</v>
+        <v>2.359</v>
       </c>
       <c r="K5" t="n">
         <v>313</v>
@@ -667,7 +667,7 @@
         <v>42</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5901</v>
+        <v>5.7306</v>
       </c>
       <c r="N5" t="n">
         <v>355</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.418</v>
+        <v>4.3197</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6038</v>
+        <v>2.5459</v>
       </c>
       <c r="D6" t="n">
-        <v>1.387</v>
+        <v>1.362</v>
       </c>
       <c r="E6" t="n">
-        <v>4.418</v>
+        <v>4.3197</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4851</v>
+        <v>3.4186</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9329</v>
+        <v>0.9011</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9029</v>
+        <v>4.8843</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9029</v>
+        <v>4.8843</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9329</v>
+        <v>0.9011</v>
       </c>
       <c r="K6" t="n">
         <v>313</v>
@@ -713,7 +713,7 @@
         <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>5.8358</v>
+        <v>5.785399999999999</v>
       </c>
       <c r="N6" t="n">
         <v>355</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.344</v>
+        <v>4.2743</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5602</v>
+        <v>2.5191</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3533</v>
+        <v>1.3414</v>
       </c>
       <c r="E7" t="n">
-        <v>4.344</v>
+        <v>4.2743</v>
       </c>
       <c r="F7" t="n">
-        <v>3.056</v>
+        <v>3.0218</v>
       </c>
       <c r="G7" t="n">
-        <v>1.288</v>
+        <v>1.2525</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9638</v>
+        <v>3.9749</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9638</v>
+        <v>3.9749</v>
       </c>
       <c r="J7" t="n">
-        <v>1.288</v>
+        <v>1.2525</v>
       </c>
       <c r="K7" t="n">
         <v>313</v>
@@ -759,7 +759,7 @@
         <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>5.2518</v>
+        <v>5.227399999999999</v>
       </c>
       <c r="N7" t="n">
         <v>355</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.175</v>
+        <v>3.1037</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8712</v>
+        <v>1.8292</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8081</v>
       </c>
       <c r="E8" t="n">
-        <v>3.175</v>
+        <v>3.1037</v>
       </c>
       <c r="F8" t="n">
-        <v>3.175</v>
+        <v>3.1037</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2242</v>
+        <v>4.1626</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2242</v>
+        <v>4.1626</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2242</v>
+        <v>4.1626</v>
       </c>
       <c r="N8" t="n">
         <v>178</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0359</v>
+        <v>2.9105</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7893</v>
+        <v>1.7154</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7578</v>
+        <v>0.7201</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0359</v>
+        <v>2.9105</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0359</v>
+        <v>2.9105</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9196</v>
+        <v>3.7199</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9196</v>
+        <v>3.7199</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9196</v>
+        <v>3.7199</v>
       </c>
       <c r="N9" t="n">
         <v>178</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9508</v>
+        <v>2.8742</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7391</v>
+        <v>1.694</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7191</v>
+        <v>0.7035</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9508</v>
+        <v>2.8742</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9566</v>
+        <v>2.9266</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0058</v>
+        <v>-0.0524</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7462</v>
+        <v>3.7567</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7462</v>
+        <v>3.7567</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0058</v>
+        <v>-0.0524</v>
       </c>
       <c r="K10" t="n">
         <v>290</v>
@@ -897,7 +897,7 @@
         <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7404</v>
+        <v>3.7043</v>
       </c>
       <c r="N10" t="n">
         <v>332</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6887</v>
+        <v>2.5767</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5846</v>
+        <v>1.5186</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5997</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6887</v>
+        <v>2.5767</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6823</v>
+        <v>2.5767</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9936</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3345</v>
+        <v>2.9548</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3345</v>
+        <v>2.9548</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9936</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>290</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3409</v>
+        <v>2.9548</v>
       </c>
       <c r="N11" t="n">
-        <v>332</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6527</v>
+        <v>2.5597</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5634</v>
+        <v>1.5086</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5834</v>
+        <v>0.5603</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6527</v>
+        <v>2.5597</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6527</v>
+        <v>3.552</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.9923</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0809</v>
+        <v>5.19</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0809</v>
+        <v>5.19</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.9923</v>
       </c>
       <c r="K12" t="n">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0809</v>
+        <v>4.1977</v>
       </c>
       <c r="N12" t="n">
-        <v>178</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6305</v>
+        <v>2.5508</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5503</v>
+        <v>1.5034</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5733</v>
+        <v>0.5562</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6305</v>
+        <v>2.5508</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6305</v>
+        <v>2.5508</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0324</v>
+        <v>2.8956</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0324</v>
+        <v>2.8956</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0324</v>
+        <v>2.8956</v>
       </c>
       <c r="N13" t="n">
         <v>155</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4743</v>
+        <v>2.4913</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4583</v>
+        <v>1.4683</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5021</v>
+        <v>0.5291</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4743</v>
+        <v>2.4913</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4743</v>
+        <v>2.4913</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6905</v>
+        <v>2.7592</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6905</v>
+        <v>2.7592</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6905</v>
+        <v>2.7592</v>
       </c>
       <c r="N14" t="n">
         <v>155</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3669</v>
+        <v>2.3265</v>
       </c>
       <c r="C15" t="n">
-        <v>1.395</v>
+        <v>1.3712</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4533</v>
+        <v>0.454</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3669</v>
+        <v>2.3265</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3669</v>
+        <v>2.3265</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4555</v>
+        <v>2.3814</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4555</v>
+        <v>2.3814</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4555</v>
+        <v>2.3814</v>
       </c>
       <c r="N15" t="n">
         <v>155</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2653</v>
+        <v>2.2195</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3351</v>
+        <v>1.3081</v>
       </c>
       <c r="D16" t="n">
-        <v>0.407</v>
+        <v>0.4053</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2653</v>
+        <v>2.2195</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2653</v>
+        <v>3.2195</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4218</v>
+        <v>4.4281</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4218</v>
+        <v>4.4281</v>
       </c>
       <c r="J16" t="n">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4218</v>
+        <v>3.4281</v>
       </c>
       <c r="N16" t="n">
         <v>332</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0396</v>
+        <v>2.0108</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2021</v>
+        <v>1.1851</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3043</v>
+        <v>0.3102</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0396</v>
+        <v>2.0108</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0074</v>
+        <v>2.9782</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9678</v>
+        <v>-0.9674</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8573</v>
+        <v>3.875</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8573</v>
+        <v>3.875</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9678</v>
+        <v>-0.9674</v>
       </c>
       <c r="K17" t="n">
         <v>290</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8895</v>
+        <v>2.9076</v>
       </c>
       <c r="N17" t="n">
         <v>332</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8291</v>
+        <v>1.5796</v>
       </c>
       <c r="C18" t="n">
-        <v>1.078</v>
+        <v>0.931</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2084</v>
+        <v>0.1138</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8291</v>
+        <v>1.5796</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8291</v>
+        <v>1.5796</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8291</v>
+        <v>1.5796</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8291</v>
+        <v>1.5796</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8291</v>
+        <v>1.5796</v>
       </c>
       <c r="N18" t="n">
         <v>261</v>
@@ -1274,32 +1274,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3776</v>
+        <v>1.2329</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8119</v>
+        <v>0.7266</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0029</v>
+        <v>-0.0441</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3776</v>
+        <v>1.2329</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3776</v>
+        <v>1.2329</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3776</v>
+        <v>1.2329</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3776</v>
+        <v>1.2329</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3776</v>
+        <v>1.2329</v>
       </c>
       <c r="N19" t="n">
         <v>261</v>
@@ -1320,32 +1320,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2355</v>
+        <v>1.2158</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7282</v>
+        <v>0.7166</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0618</v>
+        <v>-0.0519</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2355</v>
+        <v>1.2158</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2355</v>
+        <v>1.2158</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2355</v>
+        <v>1.2158</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2355</v>
+        <v>1.2158</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2355</v>
+        <v>1.2158</v>
       </c>
       <c r="N20" t="n">
         <v>261</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.202</v>
+        <v>1.1554</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7084</v>
+        <v>0.681</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.077</v>
+        <v>-0.0794</v>
       </c>
       <c r="E21" t="n">
-        <v>1.202</v>
+        <v>1.1554</v>
       </c>
       <c r="F21" t="n">
-        <v>1.202</v>
+        <v>1.1554</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.202</v>
+        <v>1.1554</v>
       </c>
       <c r="I21" t="n">
-        <v>1.202</v>
+        <v>1.1554</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.202</v>
+        <v>1.1554</v>
       </c>
       <c r="N21" t="n">
         <v>178</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.196</v>
+        <v>1.0484</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7049</v>
+        <v>0.6179</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0798</v>
+        <v>-0.1282</v>
       </c>
       <c r="E22" t="n">
-        <v>1.196</v>
+        <v>1.0484</v>
       </c>
       <c r="F22" t="n">
-        <v>1.196</v>
+        <v>1.0484</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.196</v>
+        <v>1.0484</v>
       </c>
       <c r="I22" t="n">
-        <v>1.196</v>
+        <v>1.0484</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.196</v>
+        <v>1.0484</v>
       </c>
       <c r="N22" t="n">
         <v>235</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5878</v>
+        <v>0.5083</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3464</v>
+        <v>0.2996</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3566</v>
+        <v>-0.3742</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5878</v>
+        <v>0.5083</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5878</v>
+        <v>0.5083</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5878</v>
+        <v>0.5083</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5878</v>
+        <v>0.5083</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5878</v>
+        <v>0.5083</v>
       </c>
       <c r="N23" t="n">
         <v>123</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5375</v>
+        <v>0.4811</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3168</v>
+        <v>0.2835</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3795</v>
+        <v>-0.3866</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5375</v>
+        <v>0.4811</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5375</v>
+        <v>0.4811</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5375</v>
+        <v>0.4811</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5375</v>
+        <v>0.4811</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5375</v>
+        <v>0.4811</v>
       </c>
       <c r="N24" t="n">
         <v>235</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4678</v>
+        <v>0.4178</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2757</v>
+        <v>0.2462</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4113</v>
+        <v>-0.4155</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4678</v>
+        <v>0.4178</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4678</v>
+        <v>0.4178</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4678</v>
+        <v>0.4178</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4678</v>
+        <v>0.4178</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>129</v>
+        <v>261</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4678</v>
+        <v>0.4178</v>
       </c>
       <c r="N25" t="n">
-        <v>129</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4453</v>
+        <v>0.3929</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2624</v>
+        <v>0.2316</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4215</v>
+        <v>-0.4268</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4453</v>
+        <v>0.3929</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4453</v>
+        <v>0.3929</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4453</v>
+        <v>0.3929</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4453</v>
+        <v>0.3929</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>261</v>
+        <v>129</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4453</v>
+        <v>0.3929</v>
       </c>
       <c r="N26" t="n">
-        <v>261</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2733</v>
+        <v>0.3643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611</v>
+        <v>0.2147</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4998</v>
+        <v>-0.4398</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2733</v>
+        <v>0.3643</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2733</v>
+        <v>0.3643</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2733</v>
+        <v>0.3643</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2733</v>
+        <v>0.3643</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2733</v>
+        <v>0.3643</v>
       </c>
       <c r="N27" t="n">
         <v>155</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.108</v>
+        <v>0.0119</v>
       </c>
       <c r="C28" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.575</v>
+        <v>-0.6004</v>
       </c>
       <c r="E28" t="n">
-        <v>0.108</v>
+        <v>0.0119</v>
       </c>
       <c r="F28" t="n">
-        <v>0.108</v>
+        <v>0.0119</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.108</v>
+        <v>0.0119</v>
       </c>
       <c r="I28" t="n">
-        <v>0.108</v>
+        <v>0.0119</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.108</v>
+        <v>0.0119</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1691</v>
+        <v>-0.1478</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0997</v>
+        <v>-0.0871</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7012</v>
+        <v>-0.6731</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1691</v>
+        <v>-0.1478</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1691</v>
+        <v>-0.1478</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1691</v>
+        <v>-0.1478</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1691</v>
+        <v>-0.1478</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1691</v>
+        <v>-0.1478</v>
       </c>
       <c r="N29" t="n">
         <v>235</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2538</v>
+        <v>-0.2888</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1496</v>
+        <v>-0.1702</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7397</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2538</v>
+        <v>-0.2888</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2538</v>
+        <v>-0.2888</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2538</v>
+        <v>-0.2888</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2538</v>
+        <v>-0.2888</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2538</v>
+        <v>-0.2888</v>
       </c>
       <c r="N30" t="n">
         <v>129</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3843</v>
+        <v>-0.433</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2265</v>
+        <v>-0.2552</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7991</v>
+        <v>-0.803</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3843</v>
+        <v>-0.433</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3843</v>
+        <v>-0.433</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3843</v>
+        <v>-0.433</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3843</v>
+        <v>-0.433</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3843</v>
+        <v>-0.433</v>
       </c>
       <c r="N31" t="n">
         <v>123</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4392</v>
+        <v>-0.4921</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2589</v>
+        <v>-0.29</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.83</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4392</v>
+        <v>-0.4921</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4392</v>
+        <v>-0.4921</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4392</v>
+        <v>-0.4921</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4392</v>
+        <v>-0.4921</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4392</v>
+        <v>-0.4921</v>
       </c>
       <c r="N32" t="n">
         <v>123</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7164</v>
+        <v>-0.7395</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4222</v>
+        <v>-0.4358</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9503</v>
+        <v>-0.9427</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7164</v>
+        <v>-0.7395</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7164</v>
+        <v>-0.7395</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7164</v>
+        <v>-0.7395</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7164</v>
+        <v>-0.7395</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7164</v>
+        <v>-0.7395</v>
       </c>
       <c r="N33" t="n">
         <v>235</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7776</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4489</v>
+        <v>-0.4583</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9709</v>
+        <v>-0.96</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7776</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7776</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7776</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7776</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7776</v>
       </c>
       <c r="N34" t="n">
         <v>123</v>
@@ -2010,231 +2010,231 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8082</v>
+        <v>-0.8405</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4763</v>
+        <v>-0.4954</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9921</v>
+        <v>-0.9887</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8082</v>
+        <v>-0.8405</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8082</v>
+        <v>-0.8405</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8082</v>
+        <v>-0.8405</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8082</v>
+        <v>-0.8405</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8082</v>
+        <v>-0.8405</v>
       </c>
       <c r="N35" t="n">
-        <v>129</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.478</v>
+        <v>-0.5231</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-1.0101</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>178</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1263</v>
+        <v>-1.1792</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.695</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1369</v>
+        <v>-1.143</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1263</v>
+        <v>-1.1792</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1263</v>
+        <v>-1.1792</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1263</v>
+        <v>-1.1792</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1263</v>
+        <v>-1.1792</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>261</v>
+        <v>155</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1263</v>
+        <v>-1.1792</v>
       </c>
       <c r="N37" t="n">
-        <v>261</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2309</v>
+        <v>-1.1888</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7255</v>
+        <v>-0.7006</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1845</v>
+        <v>-1.1473</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2309</v>
+        <v>-1.1888</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2309</v>
+        <v>-1.1888</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2309</v>
+        <v>-1.1888</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2309</v>
+        <v>-1.1888</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2309</v>
+        <v>-1.1888</v>
       </c>
       <c r="N38" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.238</v>
+        <v>-1.2209</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7296</v>
+        <v>-0.7196</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1878</v>
+        <v>-1.162</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.238</v>
+        <v>-1.2209</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.238</v>
+        <v>-1.2209</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.238</v>
+        <v>-1.2209</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.238</v>
+        <v>-1.2209</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>129</v>
+        <v>261</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.238</v>
+        <v>-1.2209</v>
       </c>
       <c r="N39" t="n">
-        <v>129</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.266</v>
+        <v>-1.2534</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7461</v>
+        <v>-0.7387</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2005</v>
+        <v>-1.1768</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.266</v>
+        <v>-1.2534</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.266</v>
+        <v>-1.2534</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.266</v>
+        <v>-1.2534</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.266</v>
+        <v>-1.2534</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.266</v>
+        <v>-1.2534</v>
       </c>
       <c r="N40" t="n">
         <v>129</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3789</v>
+        <v>-1.4055</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8127</v>
+        <v>-0.8284</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2519</v>
+        <v>-1.2461</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3789</v>
+        <v>-1.4055</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3789</v>
+        <v>-1.4055</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3789</v>
+        <v>-1.4055</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3789</v>
+        <v>-1.4055</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3789</v>
+        <v>-1.4055</v>
       </c>
       <c r="N41" t="n">
         <v>235</v>
@@ -2429,10 +2429,10 @@
         <v>2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J2" t="n">
-        <v>35.0607</v>
+        <v>37.6618</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.69</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3931</v>
+        <v>1.4335</v>
       </c>
       <c r="J3" t="n">
-        <v>26.4689</v>
+        <v>27.2365</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8796</v>
+        <v>0.8757</v>
       </c>
       <c r="J4" t="n">
-        <v>16.7124</v>
+        <v>16.6383</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.29</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6849</v>
+        <v>0.6662</v>
       </c>
       <c r="J5" t="n">
-        <v>13.0131</v>
+        <v>12.6578</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0128</v>
+        <v>-0.0102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2432</v>
+        <v>-0.1938</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5095</v>
+        <v>0.5234</v>
       </c>
       <c r="J7" t="n">
-        <v>9.6805</v>
+        <v>9.944599999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4231</v>
+        <v>-0.4178</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.0389</v>
+        <v>-7.9382</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.4</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5622</v>
+        <v>-0.5676</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.6818</v>
+        <v>-10.7844</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.36</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5979</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.3601</v>
+        <v>-11.5596</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.36</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5979</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.3601</v>
+        <v>-11.5596</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.59</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2601</v>
+        <v>1.2843</v>
       </c>
       <c r="J12" t="n">
-        <v>28.9823</v>
+        <v>29.5389</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1546</v>
+        <v>1.1667</v>
       </c>
       <c r="J13" t="n">
-        <v>26.5558</v>
+        <v>26.8341</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9201</v>
+        <v>0.9113</v>
       </c>
       <c r="J14" t="n">
-        <v>21.1623</v>
+        <v>20.9599</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4084</v>
+        <v>0.3768</v>
       </c>
       <c r="J15" t="n">
-        <v>9.3932</v>
+        <v>8.666399999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.15</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4084</v>
+        <v>0.3768</v>
       </c>
       <c r="J16" t="n">
-        <v>9.3932</v>
+        <v>8.666399999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.22</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5564</v>
+        <v>0.5152</v>
       </c>
       <c r="J17" t="n">
-        <v>12.7972</v>
+        <v>11.8496</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>0.132</v>
+        <v>0.1082</v>
       </c>
       <c r="J18" t="n">
-        <v>3.036</v>
+        <v>2.4886</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.62</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3957</v>
+        <v>-0.3839</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.101100000000001</v>
+        <v>-8.829700000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5014</v>
+        <v>-0.5004</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.5322</v>
+        <v>-11.5092</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.45</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5447</v>
+        <v>-0.5496</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.5281</v>
+        <v>-12.6408</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6133</v>
+        <v>0.5565</v>
       </c>
       <c r="J22" t="n">
-        <v>17.1724</v>
+        <v>15.582</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0398</v>
+        <v>-0.0309</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1144</v>
+        <v>-0.8652</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.92</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1195</v>
+        <v>-0.1021</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.346</v>
+        <v>-2.8588</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2071</v>
+        <v>-0.1868</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.7988</v>
+        <v>-5.2304</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3429</v>
+        <v>-0.3274</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.6012</v>
+        <v>-9.167199999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.43</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9932</v>
+        <v>0.9897</v>
       </c>
       <c r="J27" t="n">
-        <v>27.8096</v>
+        <v>27.7116</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8454</v>
+        <v>0.8254</v>
       </c>
       <c r="J28" t="n">
-        <v>23.6712</v>
+        <v>23.1112</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4973</v>
+        <v>0.4644</v>
       </c>
       <c r="J29" t="n">
-        <v>13.9244</v>
+        <v>13.0032</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3302</v>
+        <v>0.2977</v>
       </c>
       <c r="J30" t="n">
-        <v>9.2456</v>
+        <v>8.335599999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.11</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3302</v>
+        <v>0.2977</v>
       </c>
       <c r="J31" t="n">
-        <v>9.2456</v>
+        <v>8.335599999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2067</v>
+        <v>-0.1915</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.3407</v>
+        <v>-4.0215</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.7</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.315</v>
+        <v>-0.3024</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.615</v>
+        <v>-6.3504</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.65</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3583</v>
+        <v>-0.3464</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.5243</v>
+        <v>-7.2744</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3846</v>
+        <v>-0.3735</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.076599999999999</v>
+        <v>-7.8435</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.58</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4199</v>
+        <v>-0.4107</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.8179</v>
+        <v>-8.624700000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.58</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1659</v>
+        <v>1.1835</v>
       </c>
       <c r="J37" t="n">
-        <v>24.4839</v>
+        <v>24.8535</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.55</v>
       </c>
       <c r="I38" t="n">
-        <v>1.128</v>
+        <v>1.1451</v>
       </c>
       <c r="J38" t="n">
-        <v>23.688</v>
+        <v>24.0471</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.55</v>
       </c>
       <c r="I39" t="n">
-        <v>1.128</v>
+        <v>1.1451</v>
       </c>
       <c r="J39" t="n">
-        <v>23.688</v>
+        <v>24.0471</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.44</v>
       </c>
       <c r="I40" t="n">
-        <v>0.978</v>
+        <v>0.9819</v>
       </c>
       <c r="J40" t="n">
-        <v>20.538</v>
+        <v>20.6199</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.25</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6146</v>
+        <v>0.591</v>
       </c>
       <c r="J41" t="n">
-        <v>12.9066</v>
+        <v>12.411</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.78</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8485</v>
+        <v>0.7788</v>
       </c>
       <c r="J42" t="n">
-        <v>18.667</v>
+        <v>17.1336</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.69</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7678</v>
+        <v>0.698</v>
       </c>
       <c r="J43" t="n">
-        <v>16.8916</v>
+        <v>15.356</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.45</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5456</v>
+        <v>0.4821</v>
       </c>
       <c r="J44" t="n">
-        <v>12.0032</v>
+        <v>10.6062</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.4</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4956</v>
+        <v>0.4345</v>
       </c>
       <c r="J45" t="n">
-        <v>10.9032</v>
+        <v>9.558999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.29</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3787</v>
+        <v>0.3242</v>
       </c>
       <c r="J46" t="n">
-        <v>8.3314</v>
+        <v>7.1324</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.92</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0859</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.8898</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.87</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1465</v>
+        <v>-0.1305</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.223</v>
+        <v>-2.871</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.76</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2623</v>
+        <v>-0.248</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.7706</v>
+        <v>-5.456</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4324</v>
+        <v>-0.4238</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.5128</v>
+        <v>-9.323600000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.38</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6108</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.1626</v>
+        <v>-13.4376</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.32</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7083</v>
+        <v>0.6697</v>
       </c>
       <c r="J52" t="n">
-        <v>16.2909</v>
+        <v>15.4031</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.83</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2054</v>
+        <v>-0.1883</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.7242</v>
+        <v>-4.3309</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2153</v>
+        <v>-0.1981</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.9519</v>
+        <v>-4.5563</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4535</v>
+        <v>-0.4471</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.4305</v>
+        <v>-10.2833</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.48</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.523</v>
+        <v>-0.5253</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.029</v>
+        <v>-12.0819</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.65</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2739</v>
+        <v>1.292</v>
       </c>
       <c r="J57" t="n">
-        <v>29.2997</v>
+        <v>29.716</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.47</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0368</v>
+        <v>1.0432</v>
       </c>
       <c r="J58" t="n">
-        <v>23.8464</v>
+        <v>23.9936</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.38</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8855</v>
+        <v>0.8733</v>
       </c>
       <c r="J59" t="n">
-        <v>20.3665</v>
+        <v>20.0859</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.2</v>
       </c>
       <c r="I60" t="n">
-        <v>0.526</v>
+        <v>0.4968</v>
       </c>
       <c r="J60" t="n">
-        <v>12.098</v>
+        <v>11.4264</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.02</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0437</v>
+        <v>0.0262</v>
       </c>
       <c r="J61" t="n">
-        <v>1.0051</v>
+        <v>0.6026</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.15</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3378</v>
+        <v>0.2852</v>
       </c>
       <c r="J62" t="n">
-        <v>10.134</v>
+        <v>8.555999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1855</v>
+        <v>0.1476</v>
       </c>
       <c r="J63" t="n">
-        <v>5.565</v>
+        <v>4.428</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.04</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1203</v>
+        <v>0.092</v>
       </c>
       <c r="J64" t="n">
-        <v>3.609</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0961</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>2.883</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1151</v>
+        <v>-0.0968</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.453</v>
+        <v>-2.904</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.71</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4058</v>
+        <v>1.4368</v>
       </c>
       <c r="J67" t="n">
-        <v>42.174</v>
+        <v>43.104</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5102</v>
+        <v>0.472</v>
       </c>
       <c r="J68" t="n">
-        <v>15.306</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.09</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2949</v>
+        <v>0.2605</v>
       </c>
       <c r="J69" t="n">
-        <v>8.847</v>
+        <v>7.815</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4197</v>
+        <v>-0.3773</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.591</v>
+        <v>-11.319</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.79</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.636</v>
+        <v>-0.6011</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.08</v>
+        <v>-18.033</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4044</v>
+        <v>1.433</v>
       </c>
       <c r="J72" t="n">
-        <v>28.088</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.74</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3455</v>
+        <v>1.3718</v>
       </c>
       <c r="J73" t="n">
-        <v>26.91</v>
+        <v>27.436</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.71</v>
       </c>
       <c r="I74" t="n">
-        <v>1.31</v>
+        <v>1.3352</v>
       </c>
       <c r="J74" t="n">
-        <v>26.2</v>
+        <v>26.704</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.56</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1301</v>
+        <v>1.1521</v>
       </c>
       <c r="J75" t="n">
-        <v>22.602</v>
+        <v>23.042</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.31</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7171</v>
+        <v>0.701</v>
       </c>
       <c r="J76" t="n">
-        <v>14.342</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.6</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.3706</v>
+        <v>-0.3646</v>
       </c>
       <c r="J77" t="n">
-        <v>-7.412</v>
+        <v>-7.292</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.51</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4548</v>
+        <v>-0.4545</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.096</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.47</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4878</v>
+        <v>-0.4883</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.756</v>
+        <v>-9.766</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.43</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5221</v>
+        <v>-0.5242</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.442</v>
+        <v>-10.484</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5486</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.972</v>
+        <v>-11.058</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.23</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3804</v>
+        <v>0.3754</v>
       </c>
       <c r="J82" t="n">
-        <v>10.2708</v>
+        <v>10.1358</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1165</v>
+        <v>0.1006</v>
       </c>
       <c r="J83" t="n">
-        <v>3.1455</v>
+        <v>2.7162</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1231</v>
+        <v>-0.1047</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.3237</v>
+        <v>-2.8269</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.91</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1349</v>
+        <v>-0.1159</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.6423</v>
+        <v>-3.1293</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.86</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1904</v>
+        <v>-0.1698</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.1408</v>
+        <v>-4.5846</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.61</v>
       </c>
       <c r="I87" t="n">
-        <v>0.759</v>
+        <v>0.6905</v>
       </c>
       <c r="J87" t="n">
-        <v>20.493</v>
+        <v>18.6435</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.19</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2965</v>
+        <v>0.2418</v>
       </c>
       <c r="J88" t="n">
-        <v>8.0055</v>
+        <v>6.5286</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0796</v>
+        <v>-0.064</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.1492</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.9</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1546</v>
+        <v>-0.1346</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.1742</v>
+        <v>-3.6342</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2701</v>
+        <v>-0.2513</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.2927</v>
+        <v>-6.7851</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.22</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5997</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>17.3913</v>
+        <v>16.327</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.2</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5557</v>
+        <v>0.5179</v>
       </c>
       <c r="J93" t="n">
-        <v>16.1153</v>
+        <v>15.0191</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.14</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4186</v>
+        <v>0.3805</v>
       </c>
       <c r="J94" t="n">
-        <v>12.1394</v>
+        <v>11.0345</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.14</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4186</v>
+        <v>0.3805</v>
       </c>
       <c r="J95" t="n">
-        <v>12.1394</v>
+        <v>11.0345</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2836</v>
+        <v>-0.2434</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.224399999999999</v>
+        <v>-7.0586</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.99</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.0215</v>
+        <v>-0.016</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.464</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.98</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0393</v>
+        <v>-0.0306</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.1397</v>
+        <v>-0.8874</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.93</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1072</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.1088</v>
+        <v>-2.6332</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1191</v>
+        <v>-0.1018</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.4539</v>
+        <v>-2.9522</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.89</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1533</v>
+        <v>-0.1341</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.4457</v>
+        <v>-3.8889</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2907</v>
+        <v>0.2435</v>
       </c>
       <c r="J102" t="n">
-        <v>6.9768</v>
+        <v>5.844</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0994</v>
+        <v>-0.0854</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.3856</v>
+        <v>-2.0496</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.88</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1575</v>
+        <v>-0.1406</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.78</v>
+        <v>-3.3744</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.238</v>
+        <v>-0.2192</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.712</v>
+        <v>-5.2608</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.53</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4845</v>
+        <v>-0.4821</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.628</v>
+        <v>-11.5704</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.52</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1105</v>
+        <v>1.1231</v>
       </c>
       <c r="J107" t="n">
-        <v>26.652</v>
+        <v>26.9544</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1105</v>
+        <v>1.1231</v>
       </c>
       <c r="J108" t="n">
-        <v>26.652</v>
+        <v>26.9544</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.18</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4863</v>
+        <v>0.4555</v>
       </c>
       <c r="J109" t="n">
-        <v>11.6712</v>
+        <v>10.932</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4635</v>
+        <v>0.4323</v>
       </c>
       <c r="J110" t="n">
-        <v>11.124</v>
+        <v>10.3752</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.16</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4403</v>
+        <v>0.4087</v>
       </c>
       <c r="J111" t="n">
-        <v>10.5672</v>
+        <v>9.8088</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.85</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1426</v>
+        <v>-0.122</v>
       </c>
       <c r="J112" t="n">
-        <v>-2.5668</v>
+        <v>-2.196</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.65</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.35</v>
+        <v>-0.341</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.3</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4188</v>
+        <v>-0.4116</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.5384</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.51</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.471</v>
+        <v>-0.4667</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.478</v>
+        <v>-8.400600000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.41</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5592</v>
+        <v>-0.5644</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.0656</v>
+        <v>-10.1592</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.93</v>
       </c>
       <c r="I117" t="n">
-        <v>1.5713</v>
+        <v>1.6088</v>
       </c>
       <c r="J117" t="n">
-        <v>28.2834</v>
+        <v>28.9584</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.66</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2529</v>
+        <v>1.2757</v>
       </c>
       <c r="J118" t="n">
-        <v>22.5522</v>
+        <v>22.9626</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.57</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1446</v>
+        <v>1.1657</v>
       </c>
       <c r="J119" t="n">
-        <v>20.6028</v>
+        <v>20.9826</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.43</v>
       </c>
       <c r="I120" t="n">
-        <v>0.9483</v>
+        <v>0.9525</v>
       </c>
       <c r="J120" t="n">
-        <v>17.0694</v>
+        <v>17.145</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.37</v>
       </c>
       <c r="I121" t="n">
-        <v>0.8379</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>15.0822</v>
+        <v>14.9598</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.99</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.0416</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.92</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1046</v>
+        <v>-0.0905</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.7196</v>
+        <v>-2.353</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1287</v>
+        <v>-0.1137</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.3462</v>
+        <v>-2.9562</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.64</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3817</v>
+        <v>-0.3687</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.924200000000001</v>
+        <v>-9.5862</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.53</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4791</v>
+        <v>-0.4756</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.4566</v>
+        <v>-12.3656</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.66</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3108</v>
+        <v>1.3313</v>
       </c>
       <c r="J127" t="n">
-        <v>34.0808</v>
+        <v>34.6138</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.26</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6665</v>
+        <v>0.6371</v>
       </c>
       <c r="J128" t="n">
-        <v>17.329</v>
+        <v>16.5646</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6665</v>
+        <v>0.6371</v>
       </c>
       <c r="J129" t="n">
-        <v>17.329</v>
+        <v>16.5646</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5847</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>15.2022</v>
+        <v>14.3754</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7205</v>
+        <v>-0.6942</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.733</v>
+        <v>-18.0492</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5639</v>
+        <v>0.4943</v>
       </c>
       <c r="J132" t="n">
-        <v>13.5336</v>
+        <v>11.8632</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.33</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4388</v>
+        <v>0.3758</v>
       </c>
       <c r="J133" t="n">
-        <v>10.5312</v>
+        <v>9.0192</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.31</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4174</v>
+        <v>0.356</v>
       </c>
       <c r="J134" t="n">
-        <v>10.0176</v>
+        <v>8.544</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.2</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2942</v>
+        <v>0.2439</v>
       </c>
       <c r="J135" t="n">
-        <v>7.0608</v>
+        <v>5.8536</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.08</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1341</v>
+        <v>0.1034</v>
       </c>
       <c r="J136" t="n">
-        <v>3.2184</v>
+        <v>2.4816</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.14</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2924</v>
+        <v>0.2839</v>
       </c>
       <c r="J137" t="n">
-        <v>7.0176</v>
+        <v>6.8136</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1802</v>
+        <v>0.1654</v>
       </c>
       <c r="J138" t="n">
-        <v>4.3248</v>
+        <v>3.9696</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1455</v>
+        <v>-0.1293</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.492</v>
+        <v>-3.1032</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.55</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4661</v>
+        <v>-0.4614</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.1864</v>
+        <v>-11.0736</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4748</v>
+        <v>-0.4711</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.3952</v>
+        <v>-11.3064</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.498</v>
       </c>
       <c r="J142" t="n">
-        <v>12.6477</v>
+        <v>11.454</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1028</v>
+        <v>0.0771</v>
       </c>
       <c r="J143" t="n">
-        <v>2.3644</v>
+        <v>1.7733</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1119</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.5737</v>
+        <v>-2.2356</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.57</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4498</v>
+        <v>-0.4434</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.3454</v>
+        <v>-10.1982</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5105</v>
+        <v>-0.5117</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.7415</v>
+        <v>-11.7691</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0103</v>
+        <v>1.0096</v>
       </c>
       <c r="J147" t="n">
-        <v>23.2369</v>
+        <v>23.2208</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9597</v>
+        <v>0.9507</v>
       </c>
       <c r="J148" t="n">
-        <v>22.0731</v>
+        <v>21.8661</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5847</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>13.4481</v>
+        <v>12.7167</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.305</v>
+        <v>0.2729</v>
       </c>
       <c r="J150" t="n">
-        <v>7.015</v>
+        <v>6.2767</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.99</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.099</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-2.277</v>
+        <v>-1.8009</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7605</v>
+        <v>0.7309</v>
       </c>
       <c r="J152" t="n">
-        <v>27.378</v>
+        <v>26.3124</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.26</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6968</v>
+        <v>0.6632</v>
       </c>
       <c r="J153" t="n">
-        <v>25.0848</v>
+        <v>23.8752</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5649</v>
+        <v>0.5258</v>
       </c>
       <c r="J154" t="n">
-        <v>20.3364</v>
+        <v>18.9288</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2187</v>
+        <v>0.1867</v>
       </c>
       <c r="J155" t="n">
-        <v>7.8732</v>
+        <v>6.7212</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.032</v>
+        <v>-1.0346</v>
       </c>
       <c r="J156" t="n">
-        <v>-37.152</v>
+        <v>-37.2456</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6194</v>
+        <v>0.5601</v>
       </c>
       <c r="J157" t="n">
-        <v>22.2984</v>
+        <v>20.1636</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5883</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>21.1788</v>
+        <v>19.0332</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.1</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2469</v>
+        <v>0.2016</v>
       </c>
       <c r="J159" t="n">
-        <v>8.888400000000001</v>
+        <v>7.2576</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2653</v>
+        <v>-0.246</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.550800000000001</v>
+        <v>-8.856</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3869</v>
+        <v>-0.3758</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.9284</v>
+        <v>-13.5288</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.17</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5022</v>
+        <v>0.461</v>
       </c>
       <c r="J162" t="n">
-        <v>15.066</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.12</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3812</v>
+        <v>0.3402</v>
       </c>
       <c r="J163" t="n">
-        <v>11.436</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0925</v>
+        <v>0.0728</v>
       </c>
       <c r="J164" t="n">
-        <v>2.775</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.008</v>
+        <v>-0.0049</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.24</v>
+        <v>-0.147</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.97</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1452</v>
+        <v>-0.1149</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.356</v>
+        <v>-3.447</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8035</v>
+        <v>0.7512</v>
       </c>
       <c r="J167" t="n">
-        <v>24.105</v>
+        <v>22.536</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4456</v>
+        <v>0.3877</v>
       </c>
       <c r="J168" t="n">
-        <v>13.368</v>
+        <v>11.631</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.09</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2291</v>
+        <v>0.1853</v>
       </c>
       <c r="J169" t="n">
-        <v>6.873</v>
+        <v>5.559</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.75</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3029</v>
+        <v>-0.2853</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.087</v>
+        <v>-8.558999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.62</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4215</v>
+        <v>-0.4137</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.645</v>
+        <v>-12.411</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.58</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1994</v>
+        <v>1.2142</v>
       </c>
       <c r="J172" t="n">
-        <v>31.1844</v>
+        <v>31.5692</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.47</v>
       </c>
       <c r="I173" t="n">
-        <v>1.0505</v>
+        <v>1.0567</v>
       </c>
       <c r="J173" t="n">
-        <v>27.313</v>
+        <v>27.4742</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5162</v>
+        <v>0.4845</v>
       </c>
       <c r="J174" t="n">
-        <v>13.4212</v>
+        <v>12.597</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.03</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0939</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>2.4414</v>
+        <v>1.9084</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.03</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0939</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>2.4414</v>
+        <v>1.9084</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.19</v>
       </c>
       <c r="I177" t="n">
-        <v>0.48</v>
+        <v>0.4312</v>
       </c>
       <c r="J177" t="n">
-        <v>12.48</v>
+        <v>11.2112</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3057</v>
+        <v>0.2604</v>
       </c>
       <c r="J178" t="n">
-        <v>7.9482</v>
+        <v>6.7704</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.63</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3918</v>
+        <v>-0.3796</v>
       </c>
       <c r="J179" t="n">
-        <v>-10.1868</v>
+        <v>-9.8696</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.62</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4008</v>
+        <v>-0.3893</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.4208</v>
+        <v>-10.1218</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.49</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5148</v>
+        <v>-0.516</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.3848</v>
+        <v>-13.416</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.31</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4654</v>
+        <v>0.4698</v>
       </c>
       <c r="J182" t="n">
-        <v>13.962</v>
+        <v>14.094</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3917</v>
+        <v>0.3878</v>
       </c>
       <c r="J183" t="n">
-        <v>11.751</v>
+        <v>11.634</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1271</v>
+        <v>0.113</v>
       </c>
       <c r="J184" t="n">
-        <v>3.813</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0919</v>
+        <v>0.0795</v>
       </c>
       <c r="J185" t="n">
-        <v>2.757</v>
+        <v>2.385</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.71</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3447</v>
+        <v>-0.3304</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.341</v>
+        <v>-9.912000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.18</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2938</v>
+        <v>0.2386</v>
       </c>
       <c r="J187" t="n">
-        <v>8.814</v>
+        <v>7.158</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1557</v>
+        <v>0.118</v>
       </c>
       <c r="J188" t="n">
-        <v>4.671</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.01</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0313</v>
+        <v>0.0203</v>
       </c>
       <c r="J189" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0263</v>
+        <v>-0.0187</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.789</v>
+        <v>-0.5610000000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2238</v>
+        <v>-0.2033</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.714</v>
+        <v>-6.099</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4324</v>
+        <v>1.4594</v>
       </c>
       <c r="J192" t="n">
-        <v>28.648</v>
+        <v>29.188</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1456</v>
+        <v>1.1616</v>
       </c>
       <c r="J193" t="n">
-        <v>22.912</v>
+        <v>23.232</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.47</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0265</v>
+        <v>1.0349</v>
       </c>
       <c r="J194" t="n">
-        <v>20.53</v>
+        <v>20.698</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.28</v>
       </c>
       <c r="I195" t="n">
-        <v>0.6829</v>
+        <v>0.6623</v>
       </c>
       <c r="J195" t="n">
-        <v>13.658</v>
+        <v>13.246</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1326</v>
+        <v>0.1044</v>
       </c>
       <c r="J196" t="n">
-        <v>2.652</v>
+        <v>2.088</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3345</v>
+        <v>0.3097</v>
       </c>
       <c r="J197" t="n">
-        <v>6.69</v>
+        <v>6.194</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.73</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2855</v>
+        <v>-0.2726</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.71</v>
+        <v>-5.452</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.67</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3405</v>
+        <v>-0.3287</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.81</v>
+        <v>-6.574</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.58</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4185</v>
+        <v>-0.4095</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.25</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7064</v>
+        <v>-0.7392</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.128</v>
+        <v>-14.784</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6816</v>
+        <v>0.6475</v>
       </c>
       <c r="J202" t="n">
-        <v>20.448</v>
+        <v>19.425</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.11</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3708</v>
+        <v>0.3281</v>
       </c>
       <c r="J203" t="n">
-        <v>11.124</v>
+        <v>9.843</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.99</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0577</v>
+        <v>-0.0423</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.731</v>
+        <v>-1.269</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.82</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5387</v>
+        <v>-0.4975</v>
       </c>
       <c r="J205" t="n">
-        <v>-16.161</v>
+        <v>-14.925</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.79</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6083</v>
+        <v>-0.5698</v>
       </c>
       <c r="J206" t="n">
-        <v>-18.249</v>
+        <v>-17.094</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5554</v>
+        <v>0.4959</v>
       </c>
       <c r="J207" t="n">
-        <v>16.662</v>
+        <v>14.877</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.26</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5087</v>
+        <v>0.45</v>
       </c>
       <c r="J208" t="n">
-        <v>15.261</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.06</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1582</v>
+        <v>0.1261</v>
       </c>
       <c r="J209" t="n">
-        <v>4.746</v>
+        <v>3.783</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.03</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0882</v>
+        <v>0.0669</v>
       </c>
       <c r="J210" t="n">
-        <v>2.646</v>
+        <v>2.007</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.92</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.133</v>
+        <v>-0.1138</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.99</v>
+        <v>-3.414</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0276</v>
+        <v>1.0297</v>
       </c>
       <c r="J212" t="n">
-        <v>29.8004</v>
+        <v>29.8613</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.25</v>
       </c>
       <c r="I213" t="n">
-        <v>0.647</v>
+        <v>0.6165</v>
       </c>
       <c r="J213" t="n">
-        <v>18.763</v>
+        <v>17.8785</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6059</v>
+        <v>0.5742</v>
       </c>
       <c r="J214" t="n">
-        <v>17.5711</v>
+        <v>16.6518</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.18</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4989</v>
+        <v>0.4655</v>
       </c>
       <c r="J215" t="n">
-        <v>14.4681</v>
+        <v>13.4995</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.01</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0221</v>
+        <v>0.0122</v>
       </c>
       <c r="J216" t="n">
-        <v>0.6409</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.08</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2322</v>
+        <v>0.1876</v>
       </c>
       <c r="J217" t="n">
-        <v>6.7338</v>
+        <v>5.4404</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.05</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1658</v>
+        <v>0.1286</v>
       </c>
       <c r="J218" t="n">
-        <v>4.8082</v>
+        <v>3.7294</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0516</v>
+        <v>-0.0416</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.4964</v>
+        <v>-1.2064</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.88</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1613</v>
+        <v>-0.1426</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.6777</v>
+        <v>-4.1354</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.55</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4726</v>
+        <v>-0.4695</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.7054</v>
+        <v>-13.6155</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.88</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1284</v>
+        <v>-0.1113</v>
       </c>
       <c r="J222" t="n">
-        <v>-2.9532</v>
+        <v>-2.5599</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.75</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2678</v>
+        <v>-0.2542</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.1594</v>
+        <v>-5.8466</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.62</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3846</v>
+        <v>-0.3735</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.845800000000001</v>
+        <v>-8.5905</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4287</v>
+        <v>-0.4201</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.860099999999999</v>
+        <v>-9.6623</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4552</v>
+        <v>-0.4487</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.4696</v>
+        <v>-10.3201</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.71</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3418</v>
+        <v>1.3635</v>
       </c>
       <c r="J227" t="n">
-        <v>30.8614</v>
+        <v>31.3605</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.58</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1772</v>
+        <v>1.1927</v>
       </c>
       <c r="J228" t="n">
-        <v>27.0756</v>
+        <v>27.4321</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.57</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1643</v>
+        <v>1.1795</v>
       </c>
       <c r="J229" t="n">
-        <v>26.7789</v>
+        <v>27.1285</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.22</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5635</v>
+        <v>0.5363</v>
       </c>
       <c r="J230" t="n">
-        <v>12.9605</v>
+        <v>12.3349</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.536</v>
+        <v>-0.5032</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.328</v>
+        <v>-11.5736</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.08</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2159</v>
+        <v>0.1728</v>
       </c>
       <c r="J232" t="n">
-        <v>6.477</v>
+        <v>5.184</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0018</v>
+        <v>0.0008</v>
       </c>
       <c r="J233" t="n">
-        <v>0.054</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.99</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0244</v>
+        <v>-0.0178</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.732</v>
+        <v>-0.534</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0417</v>
+        <v>-0.032</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.251</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1997</v>
+        <v>-0.1791</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.991</v>
+        <v>-5.373</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8035</v>
+        <v>0.7772</v>
       </c>
       <c r="J237" t="n">
-        <v>24.105</v>
+        <v>23.316</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.16</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4738</v>
+        <v>0.433</v>
       </c>
       <c r="J238" t="n">
-        <v>14.214</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.15</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4501</v>
+        <v>0.4093</v>
       </c>
       <c r="J239" t="n">
-        <v>13.503</v>
+        <v>12.279</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.02</v>
       </c>
       <c r="I240" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="J240" t="n">
-        <v>2.667</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.716</v>
+        <v>-0.6853</v>
       </c>
       <c r="J241" t="n">
-        <v>-21.48</v>
+        <v>-20.559</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4025</v>
+        <v>0.3497</v>
       </c>
       <c r="J242" t="n">
-        <v>9.66</v>
+        <v>8.392799999999999</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.89</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1478</v>
+        <v>-0.1309</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.5472</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.88</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1587</v>
+        <v>-0.1413</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.8088</v>
+        <v>-3.3912</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.7</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3343</v>
+        <v>-0.3181</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.023199999999999</v>
+        <v>-7.6344</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.68</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3527</v>
+        <v>-0.3376</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.4648</v>
+        <v>-8.102399999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>2.01</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7354</v>
+        <v>1.7929</v>
       </c>
       <c r="J247" t="n">
-        <v>41.6496</v>
+        <v>43.0296</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.621</v>
+        <v>0.5926</v>
       </c>
       <c r="J248" t="n">
-        <v>14.904</v>
+        <v>14.2224</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.621</v>
+        <v>0.5926</v>
       </c>
       <c r="J249" t="n">
-        <v>14.904</v>
+        <v>14.2224</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.07</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2153</v>
+        <v>0.1862</v>
       </c>
       <c r="J250" t="n">
-        <v>5.1672</v>
+        <v>4.4688</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5445</v>
+        <v>-0.5088</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.068</v>
+        <v>-12.2112</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.01</v>
       </c>
       <c r="I252" t="n">
-        <v>0.0963</v>
+        <v>0.0781</v>
       </c>
       <c r="J252" t="n">
-        <v>2.2149</v>
+        <v>1.7963</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.85</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1812</v>
+        <v>-0.1652</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.1676</v>
+        <v>-3.7996</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.76</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2693</v>
+        <v>-0.2527</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.1939</v>
+        <v>-5.8121</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.64</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3789</v>
+        <v>-0.3659</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.714700000000001</v>
+        <v>-8.415699999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4147</v>
+        <v>-0.4044</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.5381</v>
+        <v>-9.3012</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1838</v>
+        <v>1.1987</v>
       </c>
       <c r="J257" t="n">
-        <v>27.2274</v>
+        <v>27.5701</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.45</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0067</v>
+        <v>1.0087</v>
       </c>
       <c r="J258" t="n">
-        <v>23.1541</v>
+        <v>23.2001</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.42</v>
       </c>
       <c r="I259" t="n">
-        <v>0.9575</v>
+        <v>0.9524</v>
       </c>
       <c r="J259" t="n">
-        <v>22.0225</v>
+        <v>21.9052</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.29</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7147</v>
+        <v>0.6929</v>
       </c>
       <c r="J260" t="n">
-        <v>16.4381</v>
+        <v>15.9367</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1588</v>
+        <v>-0.134</v>
       </c>
       <c r="J261" t="n">
-        <v>-3.6524</v>
+        <v>-3.082</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.52</v>
       </c>
       <c r="I262" t="n">
-        <v>0.632</v>
+        <v>0.5607</v>
       </c>
       <c r="J262" t="n">
-        <v>13.904</v>
+        <v>12.3354</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.45</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5618</v>
+        <v>0.4926</v>
       </c>
       <c r="J263" t="n">
-        <v>12.3596</v>
+        <v>10.8372</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.24</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3398</v>
+        <v>0.2855</v>
       </c>
       <c r="J264" t="n">
-        <v>7.4756</v>
+        <v>6.281</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.23</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3283</v>
+        <v>0.275</v>
       </c>
       <c r="J265" t="n">
-        <v>7.2226</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.02</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0286</v>
+        <v>0.0171</v>
       </c>
       <c r="J266" t="n">
-        <v>0.6292</v>
+        <v>0.3762</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.97</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.04</v>
+        <v>-0.0308</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.88</v>
+        <v>-0.6776</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1079</v>
+        <v>-0.0936</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.3738</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.9</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1317</v>
+        <v>-0.1164</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.8974</v>
+        <v>-2.5608</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.71</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3203</v>
+        <v>-0.3037</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.0466</v>
+        <v>-6.6814</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4288</v>
+        <v>-0.4199</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.4336</v>
+        <v>-9.2378</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4987</v>
+        <v>0.4396</v>
       </c>
       <c r="J272" t="n">
-        <v>14.961</v>
+        <v>13.188</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.12</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2894</v>
+        <v>0.2398</v>
       </c>
       <c r="J273" t="n">
-        <v>8.682</v>
+        <v>7.194</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2313</v>
+        <v>0.187</v>
       </c>
       <c r="J274" t="n">
-        <v>6.939</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.88</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.17</v>
+        <v>-0.1497</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.1</v>
+        <v>-4.491</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3392</v>
+        <v>-0.3238</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.176</v>
+        <v>-9.714</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.23</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J277" t="n">
-        <v>18.735</v>
+        <v>17.646</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.17</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4905</v>
+        <v>0.4513</v>
       </c>
       <c r="J278" t="n">
-        <v>14.715</v>
+        <v>13.539</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.11</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3482</v>
+        <v>0.3109</v>
       </c>
       <c r="J279" t="n">
-        <v>10.446</v>
+        <v>9.327</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.09</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2973</v>
+        <v>0.262</v>
       </c>
       <c r="J280" t="n">
-        <v>8.919</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.96</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.1893</v>
+        <v>-0.1548</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.679</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.05</v>
       </c>
       <c r="I282" t="n">
-        <v>0.16</v>
+        <v>0.1234</v>
       </c>
       <c r="J282" t="n">
-        <v>4.32</v>
+        <v>3.3318</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0541</v>
+        <v>-0.0434</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.4607</v>
+        <v>-1.1718</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0541</v>
+        <v>-0.0434</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.4607</v>
+        <v>-1.1718</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.5569</v>
+        <v>-2.1492</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3135</v>
+        <v>-0.296</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.464499999999999</v>
+        <v>-7.992</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.49</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1014</v>
+        <v>1.1129</v>
       </c>
       <c r="J287" t="n">
-        <v>29.7378</v>
+        <v>30.0483</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.29</v>
       </c>
       <c r="I288" t="n">
-        <v>0.7425</v>
+        <v>0.7131</v>
       </c>
       <c r="J288" t="n">
-        <v>20.0475</v>
+        <v>19.2537</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3178</v>
+        <v>0.2834</v>
       </c>
       <c r="J289" t="n">
-        <v>8.5806</v>
+        <v>7.6518</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2286</v>
+        <v>-0.1916</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.1722</v>
+        <v>-5.1732</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.93</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2885</v>
+        <v>-0.2484</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.7895</v>
+        <v>-6.7068</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.28</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5613</v>
+        <v>0.5018</v>
       </c>
       <c r="J292" t="n">
-        <v>16.839</v>
+        <v>15.054</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.13</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3066</v>
+        <v>0.2557</v>
       </c>
       <c r="J293" t="n">
-        <v>9.198</v>
+        <v>7.671</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.03</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0982</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J294" t="n">
-        <v>2.946</v>
+        <v>2.187</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.89</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1596</v>
+        <v>-0.1395</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.788</v>
+        <v>-4.185</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.75</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3024</v>
+        <v>-0.2847</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.071999999999999</v>
+        <v>-8.541</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.18</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5349</v>
+        <v>0.4938</v>
       </c>
       <c r="J297" t="n">
-        <v>16.047</v>
+        <v>14.814</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.11</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3634</v>
+        <v>0.3215</v>
       </c>
       <c r="J298" t="n">
-        <v>10.902</v>
+        <v>9.645</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0568</v>
+        <v>0.042</v>
       </c>
       <c r="J299" t="n">
-        <v>1.704</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0023</v>
+        <v>-0.0011</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5916</v>
+        <v>-0.5526</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.748</v>
+        <v>-16.578</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.23</v>
       </c>
       <c r="I302" t="n">
-        <v>0.507</v>
+        <v>0.4502</v>
       </c>
       <c r="J302" t="n">
-        <v>12.675</v>
+        <v>11.255</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.97</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.053</v>
+        <v>-0.0426</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.325</v>
+        <v>-1.065</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1405</v>
+        <v>-0.1224</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.5125</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1838</v>
+        <v>-0.164</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.595</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.64</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3947</v>
+        <v>-0.3833</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.8675</v>
+        <v>-9.5825</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.88</v>
       </c>
       <c r="I307" t="n">
-        <v>1.5941</v>
+        <v>1.6386</v>
       </c>
       <c r="J307" t="n">
-        <v>39.8525</v>
+        <v>40.965</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.25</v>
       </c>
       <c r="I308" t="n">
-        <v>0.6473</v>
+        <v>0.6167</v>
       </c>
       <c r="J308" t="n">
-        <v>16.1825</v>
+        <v>15.4175</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.21</v>
       </c>
       <c r="I309" t="n">
-        <v>0.5646</v>
+        <v>0.5319</v>
       </c>
       <c r="J309" t="n">
-        <v>14.115</v>
+        <v>13.2975</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.98</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1387</v>
+        <v>-0.1117</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.4675</v>
+        <v>-2.7925</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.79</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6518</v>
+        <v>-0.6202</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.295</v>
+        <v>-15.505</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6242</v>
+        <v>0.5763</v>
       </c>
       <c r="J312" t="n">
-        <v>15.605</v>
+        <v>14.4075</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1068</v>
+        <v>0.081</v>
       </c>
       <c r="J313" t="n">
-        <v>2.67</v>
+        <v>2.025</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.74</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2942</v>
+        <v>-0.2765</v>
       </c>
       <c r="J314" t="n">
-        <v>-7.355</v>
+        <v>-6.9125</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.7</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3315</v>
+        <v>-0.3153</v>
       </c>
       <c r="J315" t="n">
-        <v>-8.2875</v>
+        <v>-7.8825</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.44</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5605</v>
+        <v>-0.5688</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.0125</v>
+        <v>-14.22</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.59</v>
       </c>
       <c r="I317" t="n">
-        <v>1.2169</v>
+        <v>1.2324</v>
       </c>
       <c r="J317" t="n">
-        <v>30.4225</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.38</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9026</v>
+        <v>0.8871</v>
       </c>
       <c r="J318" t="n">
-        <v>22.565</v>
+        <v>22.1775</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.18</v>
       </c>
       <c r="I319" t="n">
-        <v>0.4967</v>
+        <v>0.464</v>
       </c>
       <c r="J319" t="n">
-        <v>12.4175</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.08</v>
       </c>
       <c r="I320" t="n">
-        <v>0.25</v>
+        <v>0.2196</v>
       </c>
       <c r="J320" t="n">
-        <v>6.25</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.97</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1785</v>
+        <v>-0.1476</v>
       </c>
       <c r="J321" t="n">
-        <v>-4.4625</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.92</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.1021</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>-2.3483</v>
+        <v>-2.0217</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.85</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1822</v>
+        <v>-0.1661</v>
       </c>
       <c r="J323" t="n">
-        <v>-4.1906</v>
+        <v>-3.8203</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.73</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2977</v>
+        <v>-0.2811</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.8471</v>
+        <v>-6.4653</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2977</v>
+        <v>-0.2811</v>
       </c>
       <c r="J325" t="n">
-        <v>-6.8471</v>
+        <v>-6.4653</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3527</v>
+        <v>-0.3381</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.1121</v>
+        <v>-7.7763</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.76</v>
       </c>
       <c r="I327" t="n">
-        <v>1.4079</v>
+        <v>1.4332</v>
       </c>
       <c r="J327" t="n">
-        <v>32.3817</v>
+        <v>32.9636</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.52</v>
       </c>
       <c r="I328" t="n">
-        <v>1.102</v>
+        <v>1.1155</v>
       </c>
       <c r="J328" t="n">
-        <v>25.346</v>
+        <v>25.6565</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.46</v>
       </c>
       <c r="I329" t="n">
-        <v>1.019</v>
+        <v>1.0237</v>
       </c>
       <c r="J329" t="n">
-        <v>23.437</v>
+        <v>23.5451</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.33</v>
       </c>
       <c r="I330" t="n">
-        <v>0.7903</v>
+        <v>0.7734</v>
       </c>
       <c r="J330" t="n">
-        <v>18.1769</v>
+        <v>17.7882</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.76</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7398</v>
+        <v>-0.7191</v>
       </c>
       <c r="J331" t="n">
-        <v>-17.0154</v>
+        <v>-16.5393</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.79</v>
       </c>
       <c r="I332" t="n">
-        <v>1.4219</v>
+        <v>1.4488</v>
       </c>
       <c r="J332" t="n">
-        <v>29.8599</v>
+        <v>30.4248</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.69</v>
       </c>
       <c r="I333" t="n">
-        <v>1.3004</v>
+        <v>1.3218</v>
       </c>
       <c r="J333" t="n">
-        <v>27.3084</v>
+        <v>27.7578</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.5</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0628</v>
+        <v>1.078</v>
       </c>
       <c r="J334" t="n">
-        <v>22.3188</v>
+        <v>22.638</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.5</v>
       </c>
       <c r="I335" t="n">
-        <v>1.0628</v>
+        <v>1.078</v>
       </c>
       <c r="J335" t="n">
-        <v>22.3188</v>
+        <v>22.638</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.98</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1801</v>
+        <v>-0.1594</v>
       </c>
       <c r="J336" t="n">
-        <v>-3.7821</v>
+        <v>-3.3474</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.82</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1693</v>
+        <v>-0.1486</v>
       </c>
       <c r="J337" t="n">
-        <v>-3.5553</v>
+        <v>-3.1206</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.307</v>
+        <v>-0.2963</v>
       </c>
       <c r="J338" t="n">
-        <v>-6.447</v>
+        <v>-6.2223</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.59</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3998</v>
+        <v>-0.3931</v>
       </c>
       <c r="J339" t="n">
-        <v>-8.395799999999999</v>
+        <v>-8.255100000000001</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.43</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5402</v>
       </c>
       <c r="J340" t="n">
-        <v>-11.2938</v>
+        <v>-11.3442</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.34</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6177</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J341" t="n">
-        <v>-12.9717</v>
+        <v>-13.2636</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1952</v>
+        <v>1.2099</v>
       </c>
       <c r="J342" t="n">
-        <v>27.4896</v>
+        <v>27.8277</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.35</v>
       </c>
       <c r="I343" t="n">
-        <v>0.849</v>
+        <v>0.8285</v>
       </c>
       <c r="J343" t="n">
-        <v>19.527</v>
+        <v>19.0555</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.29</v>
       </c>
       <c r="I344" t="n">
-        <v>0.7295</v>
+        <v>0.7019</v>
       </c>
       <c r="J344" t="n">
-        <v>16.7785</v>
+        <v>16.1437</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.99</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.0965</v>
+        <v>-0.0757</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.2195</v>
+        <v>-1.7411</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.89</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4096</v>
+        <v>-0.369</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.4208</v>
+        <v>-8.487</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.98</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.0273</v>
+        <v>-0.0201</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.6279</v>
+        <v>-0.4623</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.98</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.0273</v>
+        <v>-0.0201</v>
       </c>
       <c r="J348" t="n">
-        <v>-0.6279</v>
+        <v>-0.4623</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.92</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1107</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.5461</v>
+        <v>-2.2126</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3411</v>
+        <v>-0.3254</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.8453</v>
+        <v>-7.4842</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.63</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3956</v>
+        <v>-0.3837</v>
       </c>
       <c r="J351" t="n">
-        <v>-9.098800000000001</v>
+        <v>-8.825100000000001</v>
       </c>
     </row>
   </sheetData>
